--- a/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>DY</t>
   </si>
@@ -656,417 +656,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45318</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45227</v>
+      </c>
+      <c r="F7" s="2">
         <v>45136</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45045</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44863</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44772</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44590</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44499</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44317</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44226</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44128</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44037</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43946</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43855</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43764</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43673</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43582</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43491</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43400</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43309</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43218</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43127</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43036</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42945</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42854</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42763</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42672</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>952500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1136100</v>
+      </c>
+      <c r="F8" s="3">
         <v>1041500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1045500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>917500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1042400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>972300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>876300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>761500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>854000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>787600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>727500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>750700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>810300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>823900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>814300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>737600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>884100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>884200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>833700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>748600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>848200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>799500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>731400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>655100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>756200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>780200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>786300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>701100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>799200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>789200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>791400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>886700</v>
+      </c>
+      <c r="F9" s="3">
         <v>830400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>853400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>765700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>850900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>798000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>745700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>656600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>705900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>651400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>620000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>645500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>658400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>658000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>680200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>633200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>724400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>720400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>701800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>633300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>687200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>642400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>599600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>540600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>600800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>606900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>621500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>561400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>615000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>605900</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>161100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>249400</v>
+      </c>
+      <c r="F10" s="3">
         <v>211100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>192100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>151800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>191500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>174300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>130600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>104900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>148100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>136200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>107500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>105200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>151900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>165900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>134100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>104400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>159700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>163800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>131900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>115300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>161000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>157100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>131800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>114500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>155400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>173300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>164800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>139700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>184200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>183300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1099,8 +1125,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1191,8 +1219,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1283,19 +1317,25 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1303,41 +1343,41 @@
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>40800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>100</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1348,11 +1388,11 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1363,112 +1403,124 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>42500</v>
+      </c>
+      <c r="F15" s="3">
         <v>38000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>37300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>36700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>35500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>35300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>36600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>37300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>37800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>38500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>39100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>43600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>42300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>44100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>45900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>46600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>47400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>47200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>46300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>45900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>45500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>44800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>43400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>42400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>42700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>40200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>37400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>35700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>34500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,192 +1550,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>909700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1016700</v>
+      </c>
+      <c r="F17" s="3">
         <v>953200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>973000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>874400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>965100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>906700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>851700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>757800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>810500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>754600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>726200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>753000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>763300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>769900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>832700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>740900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>841600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>832700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>806700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>752700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>801500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>751700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>705200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>643400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>708100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>706700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>720200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>655300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>709700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>704100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>42800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>119400</v>
+      </c>
+      <c r="F18" s="3">
         <v>88300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>72500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>43100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>77300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>65600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>24600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>3700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>43500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>33000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>47000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>54000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-18400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-3300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>42500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>51500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>27000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-4100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>46700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>47800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>26200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>11700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>48100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>73500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>66100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>45800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>89500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1716,468 +1782,500 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E20" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F20" s="3">
         <v>5800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>4800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>2700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>3700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>3100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>4000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>5700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>2900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>4100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>7700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>5900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>6000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>4800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>1000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>92100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>168800</v>
+      </c>
+      <c r="F21" s="3">
         <v>132000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>114700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>80200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>115200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>103500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>66000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>41200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>81800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>72500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>43100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>42000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>93000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>101300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>28600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>43900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>91300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>102700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>79100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>43000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>95100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>96700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>77200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>54400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>96700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>119800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>108300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>82600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>125000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>124700</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F22" s="3">
         <v>12300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>11400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>11600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>10600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>9300</v>
-      </c>
-      <c r="I22" s="3">
-        <v>9100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>8800</v>
       </c>
       <c r="K22" s="3">
         <v>9100</v>
       </c>
       <c r="L22" s="3">
+        <v>8800</v>
+      </c>
+      <c r="M22" s="3">
+        <v>9100</v>
+      </c>
+      <c r="N22" s="3">
         <v>9300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>5900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>4700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>4700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>7900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>12500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>12600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>13100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>12900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>12200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>12400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>11300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>10400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>10200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>9900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>9700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>9700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>9400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>9200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>9100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>112400</v>
+      </c>
+      <c r="F23" s="3">
         <v>81800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>66100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>31900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>69200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>58900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>20200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-4900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>34900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>24700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-6300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>46000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>49300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-29700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-15300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>30800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>42600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>20500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-15400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>38300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>41400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>23700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>2200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>44400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>69800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>61500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>37700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>81400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E24" s="3">
+        <v>28600</v>
+      </c>
+      <c r="F24" s="3">
         <v>21500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>14600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>7100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>15100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>15000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-5700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>6200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>6500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-2700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>12000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>12200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>2700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-5200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>6600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>12700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>6200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-3300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>10500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>11500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>6500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>15600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>26100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>22800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>14000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>30300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>29600</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2268,192 +2366,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>83700</v>
+      </c>
+      <c r="F26" s="3">
         <v>60200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>51500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>24800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>54000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>43900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>19500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>28700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>18200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-6800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>33900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>37000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-32400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-10100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>24200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>29900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>14300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-12100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>27800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>29900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>17200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>7900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>28800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>43700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>38800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>23700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>51100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>83700</v>
+      </c>
+      <c r="F27" s="3">
         <v>60200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>51500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>24800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>54000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>43900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>19500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>28700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>18200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-6800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>33900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>37000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-32400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-10100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>24200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>29900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>14300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-12100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>27800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>29900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>17200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>7900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>28800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>43700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>38800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>23700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>51100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2544,8 +2660,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2579,50 +2701,50 @@
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>2600</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>2600</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
-        <v>-1100</v>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>-1100</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>32200</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>32200</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2636,8 +2758,14 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2856,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,192 +2954,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-5800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-4800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-2700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-3700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-4000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-5700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-2900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>83700</v>
+      </c>
+      <c r="F33" s="3">
         <v>60200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>51500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>24800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>54000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>43900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>19500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>28700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>18200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-4200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>33900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>37000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-32400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-11200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>24200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>29900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>14300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-12100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>27800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>29900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>17200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>40100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>28800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>43700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>38800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>23700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>51100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,197 +3248,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>83700</v>
+      </c>
+      <c r="F35" s="3">
         <v>60200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>51500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>24800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>54000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>43900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>19500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>28700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>18200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-4200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>33900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>37000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-32400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-11200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>24200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>29900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>14300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-12100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>27800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>29900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>17200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>40100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>28800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>43700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>38800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>23700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>51100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45318</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45227</v>
+      </c>
+      <c r="F38" s="2">
         <v>45136</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45045</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44954</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44863</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44772</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44590</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44499</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44317</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44226</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44128</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44037</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43946</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43855</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43764</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43673</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43582</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43491</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43400</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43309</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43218</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43127</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43036</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42945</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42854</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42763</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42672</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3489,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,100 +3525,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>101100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F41" s="3">
         <v>83400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>71400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>224200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>65300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>120300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>185600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>310800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>263700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>261900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>330600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>11800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>12000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>22500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>643900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>54600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>11800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>12600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>33600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>128300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>21500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>23900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>57900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>84000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>24500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>38600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>19400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>29500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>21700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3537,444 +3717,474 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1298700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1534900</v>
+      </c>
+      <c r="F43" s="3">
         <v>1303300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1242800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1114900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1297800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1170700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1043300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>933200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1077900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1102800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1048500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1057000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1144300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1156600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1145800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1073600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1262900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1156800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1001900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>844600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1003300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>863500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>763100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>332600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>349600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>377300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>355100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>335500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>329800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>108600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>114000</v>
+      </c>
+      <c r="F44" s="3">
         <v>117200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>115700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>115000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>107100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>98900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>94100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>81300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>69900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>69700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>71100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>70800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>70800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>77800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>92600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>98300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>104900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>107400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>105200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>94400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>90800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>87800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>84300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>448500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>490400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>472500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>529100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>481600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>570000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>450600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>44100</v>
+      </c>
+      <c r="F45" s="3">
         <v>51300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>53900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>38600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>42800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>43900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>47000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>30900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>37500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>43300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>47900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>29000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>38400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>49700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>48600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>31800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>32300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>31100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>37800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>29100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>33300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>30100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>30800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>39700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>28800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>50100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>46700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>41700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>45400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1550000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1708700</v>
+      </c>
+      <c r="F46" s="3">
         <v>1555200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1483800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1492700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1513000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1433800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1370000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1356100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1449000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1477700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1498100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1168600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1265500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1306600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1930900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1258300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1411900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1307800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1178500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1096400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1148900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1005300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>936100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>904800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>893400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>938500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>950200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>888300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>966900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>851200</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F47" s="3">
         <v>5300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>6800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>8300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>9600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>11000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>12500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>14100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>15300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>16700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>16200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>17600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>18600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>19900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>21300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>22700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>24200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>26200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>28400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>55200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>32000</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>8</v>
@@ -3997,192 +4207,210 @@
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>521300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>505100</v>
+      </c>
+      <c r="F48" s="3">
         <v>466000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>447100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>435100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>403300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>377600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>361100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>355900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>346200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>343600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>340500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>337100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>354200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>385500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>422100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>446200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>463000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>491700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>498400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>424800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>428300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>423700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>416300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>414800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>423300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>422100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>378400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>344100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>337700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>420900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>425700</v>
+      </c>
+      <c r="F49" s="3">
         <v>352100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>355600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>359100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>362600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>366500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>370400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>374300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>378300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>382500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>387100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>391800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>397000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>402000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>407200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>465700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>470900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>476200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>481500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>486900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>492300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>498100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>503900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>493200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>499100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>505300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>513100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>498200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>500300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>508000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4501,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,100 +4599,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>20800</v>
+      </c>
+      <c r="F52" s="3">
         <v>16900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>18400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>18000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>16800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>17500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>18100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>17900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>15800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>21400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>21100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>29000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>29700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>30600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>31400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>24800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>25500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>26400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>24400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>34200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>31700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>25400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>26800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>28200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>36800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>33400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>34300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>35800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>33500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,100 +4795,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2516900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2664200</v>
+      </c>
+      <c r="F54" s="3">
         <v>2395600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2311700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2313300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2305300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2206400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2132100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2118200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2204700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2241900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2263000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1944200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2065100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2144700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2812900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2217600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2395600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2328400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2211200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2097500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2133200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1952400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1883000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1841000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1852500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1899300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1876000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1766400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1838400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1719700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +4933,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,100 +4969,108 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>222100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>215300</v>
+      </c>
+      <c r="F57" s="3">
         <v>204800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>196200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>207700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>201000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>187600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>176400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>155900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>173600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>173200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>171000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>159000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>183700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>177300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>194400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>119600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>129500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>140300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>138700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>119500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>134700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>125700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>112200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>92400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>109900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>133000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>119300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>99300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>114700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>115500</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4828,25 +5096,25 @@
         <v>17500</v>
       </c>
       <c r="K58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="L58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="M58" s="3">
         <v>13100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>66600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>61500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>81700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>78100</v>
-      </c>
-      <c r="P58" s="3">
-        <v>22500</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>22500</v>
       </c>
       <c r="R58" s="3">
         <v>22500</v>
@@ -4855,414 +5123,444 @@
         <v>22500</v>
       </c>
       <c r="T58" s="3">
+        <v>22500</v>
+      </c>
+      <c r="U58" s="3">
+        <v>22500</v>
+      </c>
+      <c r="V58" s="3">
         <v>16900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>11300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>5600</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>31300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>28900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>26500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>24100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>21700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>14400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>18800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>17500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>266700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>256000</v>
+      </c>
+      <c r="F59" s="3">
         <v>237200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>219400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>244300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>252600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>227100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>201700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>208400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>206400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>207600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>203500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>207800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>201900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>211500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>211400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>180900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>212800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>199800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>191700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>159900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>169300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>153300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>134800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>140800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>149200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>163900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>155100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>145000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>179700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>506300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>488800</v>
+      </c>
+      <c r="F60" s="3">
         <v>459400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>433100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>469600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>471100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>432100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>395700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>381800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>393200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>447500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>436100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>448500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>463700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>411300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>428300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>323000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>364800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>357000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>341700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>285000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>304000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>310300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>275900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>259600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>283100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>318500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>288900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>263200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>312000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>322600</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>791400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>949400</v>
+      </c>
+      <c r="F61" s="3">
         <v>799400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>803400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>807400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>811400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>815300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>819300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>823300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>827200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>831200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>835200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>501600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>490000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>665500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1363900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>844400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>970200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>932300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>867400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>867600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>867800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>727300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>731700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>733800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>736000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>738300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>811600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>740600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>774500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>706200</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>164500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>172000</v>
+      </c>
+      <c r="F62" s="3">
         <v>172700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>177800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>167600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>164200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>161900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>158800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>154600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>173500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>182700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>181800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>182800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>198200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>194100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>186800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>181600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>180400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>185700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>181000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>140800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>144500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>131500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>128400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>122500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>143800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>170900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>152800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>147600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>138200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5651,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5445,8 +5749,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,100 +5847,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1462200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1610200</v>
+      </c>
+      <c r="F66" s="3">
         <v>1431600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1414300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1444500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1446700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1409400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1373800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1359700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1393900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1461400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1453100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1132900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1151900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1270900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1979000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1349000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1515400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1474900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1390000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1293300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1316400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1169200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1136000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1116000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1162900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1227700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1253300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1151400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1224700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1162400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +5985,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +6079,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6177,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5939,8 +6275,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,100 +6373,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1040300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1026600</v>
+      </c>
+      <c r="F72" s="3">
         <v>942800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>882600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>855100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>838300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>784300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>747100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>748400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>798500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>769800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>797700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>800600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>867800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>833800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>796800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>829700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>840900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>816700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>786800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>772500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>784500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>756700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>726800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>709600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>674200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>652300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>608600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>600500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>588900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>537900</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6569,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +6667,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,100 +6765,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1054700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1053900</v>
+      </c>
+      <c r="F76" s="3">
         <v>964000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>897400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>868800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>858600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>797000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>758300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>758500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>810800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>780400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>810000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>811300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>913100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>873700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>833900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>868600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>880200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>853400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>821200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>804200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>816900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>783200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>747000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>725000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>689600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>671600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>622700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>615100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>613700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>557300</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,197 +6961,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45318</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45227</v>
+      </c>
+      <c r="F80" s="2">
         <v>45136</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45045</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44954</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44863</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44772</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44590</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44499</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44317</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44226</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44128</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44037</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43946</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43855</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43764</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43673</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43582</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43491</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43400</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43309</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43218</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43127</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43036</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42945</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42854</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42763</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42672</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>83700</v>
+      </c>
+      <c r="F81" s="3">
         <v>60200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>51500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>24800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>54000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>43900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>19500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>28700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>18200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-4200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>33900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>37000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-32400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-11200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>24200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>29900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>14300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-12100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>27800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>29900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>17200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>40100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>28800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>43700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>38800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>23700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>51100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,100 +7202,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>42500</v>
+      </c>
+      <c r="F83" s="3">
         <v>38000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>37300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>36700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>35500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>35300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>36600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>37300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>37800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>38500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>39100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>43600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>42300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>44100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>45900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>46600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>47400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>47200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>46300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>45900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>45500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>44800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>43400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>42400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>42700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>40200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>37400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>35700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>34500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7394,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7492,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +7590,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +7688,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,100 +7786,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>325100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="F89" s="3">
         <v>56300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-85100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>246200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-4500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-12000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-64900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>145500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>104300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>17300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>41500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>102400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>111900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>82300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>85200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>191800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-24000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-53600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-56100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>142800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-55500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>12600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>24600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>103700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>56800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>149900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>42300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>105800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-41600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>182500</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,100 +7924,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-57400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-67200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-51000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-42900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-65200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-54800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-42500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-38400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-43600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-45100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-36700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-31600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-21900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-9400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-20700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-18700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-17900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-38200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-45800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-37200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-47300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-46000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-34500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-31800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-58300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-40100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-47300</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +8116,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,100 +8214,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-52700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-179900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-40000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-33600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-62600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-49200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-39100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-33000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-43400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-44100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-35500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-28600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-20400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-3500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-18300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-15800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-14500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-32500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-38400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-33800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-42600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-39100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-45800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-78400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-32900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-38200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-151600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,8 +8352,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7978,8 +8446,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +8544,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +8642,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,100 +8740,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-187000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>149500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-4300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-34100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-24700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-1300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-14200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-27200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-55100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-58400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-50400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>305900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-85500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-119000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-701200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>522300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-133200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>37800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>65100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-3100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>95700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-22800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>25900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-65100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>67700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-16500</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8438,96 +8936,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>85400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-67700</v>
+      </c>
+      <c r="F102" s="3">
         <v>12000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-152800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>158900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-55000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-65300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-125200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>47100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-68700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>318800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-10500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-621300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>589100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>42700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-21000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-95300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>105800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-2400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-33400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-26100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>59500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>19300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>7800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-12100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>14500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>DY</t>
   </si>
@@ -656,443 +656,455 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45409</v>
+      </c>
+      <c r="E7" s="2">
         <v>45318</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45227</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45136</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45045</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44954</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44863</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44772</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44590</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44499</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44317</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44226</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44128</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44037</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43946</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43855</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43764</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43673</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43582</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43491</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43400</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43309</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43218</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43127</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43036</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42945</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42854</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42763</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42672</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1142400</v>
+      </c>
+      <c r="E8" s="3">
         <v>952500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1136100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1041500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1045500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>917500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1042400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>972300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>876300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>761500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>854000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>787600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>727500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>750700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>810300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>823900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>814300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>737600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>884100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>884200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>833700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>748600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>848200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>799500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>731400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>655100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>756200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>780200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>786300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>701100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>799200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>789200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>921600</v>
+      </c>
+      <c r="E9" s="3">
         <v>791400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>886700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>830400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>853400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>765700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>850900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>798000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>745700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>656600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>705900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>651400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>620000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>645500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>658400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>658000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>680200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>633200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>724400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>720400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>701800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>633300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>687200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>642400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>599600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>540600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>600800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>606900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>621500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>561400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>615000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>605900</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>220800</v>
+      </c>
+      <c r="E10" s="3">
         <v>161100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>249400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>211100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>192100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>151800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>191500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>174300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>130600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>104900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>148100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>136200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>107500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>105200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>151900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>165900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>134100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>104400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>159700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>163800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>131900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>115300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>161000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>157100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>131800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>114500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>155400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>173300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>164800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>139700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>184200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>183300</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1127,8 +1139,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1225,8 +1238,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1323,16 +1339,19 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1340,14 +1359,14 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1355,32 +1374,32 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>40800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>100</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1394,8 +1413,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1409,118 +1428,124 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E15" s="3">
         <v>45300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>42500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>38000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>37300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>36700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>35500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>35300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>36600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>37300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>37800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>38500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>39100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>43600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>42300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>44100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>45900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>46600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>47400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>47200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>46300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>45900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>45500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>44800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>43400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>42400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>42700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>40200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>37400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>35700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>34500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1552,204 +1577,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1061400</v>
+      </c>
+      <c r="E17" s="3">
         <v>909700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1016700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>953200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>973000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>874400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>965100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>906700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>851700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>757800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>810500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>754600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>726200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>753000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>763300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>769900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>832700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>740900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>841600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>832700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>806700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>752700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>801500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>751700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>705200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>643400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>708100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>706700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>720200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>655300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>709700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>704100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E18" s="3">
         <v>42800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>119400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>88300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>72500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>43100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>77300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>65600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>24600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>43500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>33000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>47000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>54000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-18400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>42500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>51500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>27000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>46700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>47800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>26200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>48100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>73500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>66100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>45800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>89500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1784,498 +1816,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E20" s="3">
         <v>3900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>4100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>7700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>5900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>6000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>4800</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>1000</v>
       </c>
       <c r="AG20" s="3">
         <v>1000</v>
       </c>
       <c r="AH20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>135500</v>
+      </c>
+      <c r="E21" s="3">
         <v>92100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>168800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>132000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>114700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>80200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>115200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>103500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>66000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>41200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>81800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>72500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>43100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>42000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>93000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>101300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>28600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>43900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>91300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>102700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>79100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>43000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>95100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>96700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>77200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>54400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>96700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>119800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>108300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>82600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>125000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>124700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E22" s="3">
         <v>15000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>5900</v>
-      </c>
-      <c r="P22" s="3">
-        <v>4700</v>
       </c>
       <c r="Q22" s="3">
         <v>4700</v>
       </c>
       <c r="R22" s="3">
+        <v>4700</v>
+      </c>
+      <c r="S22" s="3">
         <v>7900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>13100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>11300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9900</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>9700</v>
       </c>
       <c r="AD22" s="3">
         <v>9700</v>
       </c>
       <c r="AE22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AF22" s="3">
         <v>9400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E23" s="3">
         <v>31800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>112400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>81800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>66100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>31900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>69200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>58900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>20200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>34900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>24700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>46000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>49300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-29700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-15300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>30800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>42600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>20500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-15400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>38300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>41400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>23700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>44400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>69800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>61500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>37700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>81400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E24" s="3">
         <v>8400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>28600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>21500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>15100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-5700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>12000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-5200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>12700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>10500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>11500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>15600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>26100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>22800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>14000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>30300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>29600</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2372,204 +2420,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E26" s="3">
         <v>23400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>83700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>60200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>51500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>24800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>54000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>43900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>28700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>33900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>37000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-32400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>24200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>29900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>14300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-12100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>27800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>29900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>17200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>28800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>43700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>38800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>23700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>51100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E27" s="3">
         <v>23400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>83700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>60200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>51500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>24800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>54000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>43900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>33900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>37000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-32400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>24200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>29900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>14300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>27800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>29900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>17200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>28800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>43700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>38800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>23700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>51100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2666,31 +2723,34 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -2707,11 +2767,11 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3">
         <v>2600</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2719,11 +2779,11 @@
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3">
         <v>-1100</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2731,11 +2791,11 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
+      <c r="X29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2743,11 +2803,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>32200</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2764,8 +2824,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2862,8 +2925,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2960,204 +3026,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AG32" s="3">
         <v>-1000</v>
       </c>
       <c r="AH32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E33" s="3">
         <v>23400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>83700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>60200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>51500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>24800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>54000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>43900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>28700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>33900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>37000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-32400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>24200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>29900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>14300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-12100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>27800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>29900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>17200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>40100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>28800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>43700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>38800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>23700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>51100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3254,209 +3329,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E35" s="3">
         <v>23400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>83700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>60200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>51500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>24800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>54000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>43900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>28700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>33900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>37000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-32400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>24200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>29900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>14300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-12100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>27800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>29900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>17200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>40100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>28800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>43700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>38800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>23700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>51100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45409</v>
+      </c>
+      <c r="E38" s="2">
         <v>45318</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45227</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45136</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45045</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44954</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44863</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44772</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44590</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44499</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44317</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44226</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44128</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44037</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43946</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43855</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43764</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43673</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43582</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43491</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43400</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43309</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43218</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43127</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43036</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42945</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42854</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42763</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42672</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3491,8 +3575,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3527,106 +3612,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E41" s="3">
         <v>101100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>83400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>71400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>224200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>65300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>120300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>185600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>310800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>263700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>261900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>330600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>643900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>54600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>33600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>128300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>21500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>23900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>57900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>84000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>24500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>38600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>19400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>29500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>21700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3723,471 +3812,486 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1442300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1298700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1534900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1303300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1242800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1114900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1297800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1170700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1043300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>933200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1077900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1102800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1048500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1057000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1144300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1156600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1145800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1073600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1262900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1156800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1001900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>844600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1003300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>863500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>763100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>332600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>349600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>377300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>355100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>335500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>329800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E44" s="3">
         <v>108600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>114000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>117200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>115700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>115000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>107100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>98900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>94100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>81300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>69900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>69700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>71100</v>
-      </c>
-      <c r="P44" s="3">
-        <v>70800</v>
       </c>
       <c r="Q44" s="3">
         <v>70800</v>
       </c>
       <c r="R44" s="3">
+        <v>70800</v>
+      </c>
+      <c r="S44" s="3">
         <v>77800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>92600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>98300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>104900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>107400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>105200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>94400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>90800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>87800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>84300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>448500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>490400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>472500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>529100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>481600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>570000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>450600</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E45" s="3">
         <v>41700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>44100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>51300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>53900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>38600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>42800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>43900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>47000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>37500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>43300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>47900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>29000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>38400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>49700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>48600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>31800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>32300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>31100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>37800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>29100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>33300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>30100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>30800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>39700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>28800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>50100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>46700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>41700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>45400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1626800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1550000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1708700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1555200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1483800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1492700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1513000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1433800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1370000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1356100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1449000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1477700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1498100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1168600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1265500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1306600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1930900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1258300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1411900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1307800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1178500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1096400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1148900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1005300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>936100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>904800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>893400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>938500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>950200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>888300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>966900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>851200</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E47" s="3">
         <v>2600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>14100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>15300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>16700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>16200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>17600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>18600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>19900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>21300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>22700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>24200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>26200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>28400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>55200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>32000</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA47" s="3" t="s">
         <v>8</v>
@@ -4213,204 +4317,213 @@
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>538700</v>
+      </c>
+      <c r="E48" s="3">
         <v>521300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>505100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>466000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>447100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>435100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>403300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>377600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>361100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>355900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>346200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>343600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>340500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>337100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>354200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>385500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>422100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>446200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>463000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>491700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>498400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>424800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>428300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>423700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>416300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>414800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>423300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>422100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>378400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>344100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>337700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>423800</v>
+      </c>
+      <c r="E49" s="3">
         <v>420900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>425700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>352100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>355600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>359100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>362600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>366500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>370400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>374300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>378300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>382500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>387100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>391800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>397000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>402000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>407200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>465700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>470900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>476200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>481500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>486900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>492300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>498100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>503900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>493200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>499100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>505300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>513100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>498200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>500300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>508000</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4507,8 +4620,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4605,106 +4721,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E52" s="3">
         <v>22000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>18400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>18000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>17500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>21400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>21100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>31400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>24800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>25500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>24400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>34200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>31700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>25400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>26800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>28200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>36800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>33400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>34300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>35800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>33500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4801,106 +4923,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2611600</v>
+      </c>
+      <c r="E54" s="3">
         <v>2516900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2664200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2395600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2311700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2313300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2305300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2206400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2132100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2118200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2204700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2241900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2263000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1944200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2065100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2144700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2812900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2217600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2395600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2328400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2211200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2097500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2133200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1952400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1883000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1841000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1852500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1899300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1876000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1766400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1838400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1719700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4935,8 +5063,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4971,106 +5100,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>212900</v>
+      </c>
+      <c r="E57" s="3">
         <v>222100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>215300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>204800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>196200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>207700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>201000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>187600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>176400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>155900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>173600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>173200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>171000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>159000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>183700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>177300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>194400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>119600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>129500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>140300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>138700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>119500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>134700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>125700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>112200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>92400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>109900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>133000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>119300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>99300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>114700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>115500</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5102,22 +5235,22 @@
         <v>17500</v>
       </c>
       <c r="M58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="N58" s="3">
         <v>13100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>66600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>61500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>81700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>78100</v>
-      </c>
-      <c r="R58" s="3">
-        <v>22500</v>
       </c>
       <c r="S58" s="3">
         <v>22500</v>
@@ -5129,438 +5262,453 @@
         <v>22500</v>
       </c>
       <c r="V58" s="3">
+        <v>22500</v>
+      </c>
+      <c r="W58" s="3">
         <v>16900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>11300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5600</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>31300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>28900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>26500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>24100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>21700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>14400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>18800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>17500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>283200</v>
+      </c>
+      <c r="E59" s="3">
         <v>266700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>256000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>237200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>219400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>244300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>252600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>227100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>201700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>208400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>206400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>207600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>203500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>207800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>201900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>211500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>211400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>180900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>212800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>199800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>191700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>159900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>169300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>153300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>134800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>140800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>149200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>163900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>155100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>145000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>179700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>513600</v>
+      </c>
+      <c r="E60" s="3">
         <v>506300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>488800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>459400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>433100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>469600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>471100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>432100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>395700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>381800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>393200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>447500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>436100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>448500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>463700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>411300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>428300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>323000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>364800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>357000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>341700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>285000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>304000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>310300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>275900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>259600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>283100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>318500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>288900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>263200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>312000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>322600</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>842400</v>
+      </c>
+      <c r="E61" s="3">
         <v>791400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>949400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>799400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>803400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>807400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>811400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>815300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>819300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>823300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>827200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>831200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>835200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>501600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>490000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>665500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1363900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>844400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>970200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>932300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>867400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>867600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>867800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>727300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>731700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>733800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>736000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>738300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>811600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>740600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>774500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>706200</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E62" s="3">
         <v>164500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>172000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>172700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>177800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>167600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>164200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>161900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>158800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>154600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>173500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>182700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>181800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>182800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>198200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>194100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>186800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>181600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>180400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>185700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>181000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>140800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>144500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>131500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>128400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>122500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>143800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>170900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>152800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>147600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>138200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5657,8 +5805,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5755,8 +5906,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5853,106 +6007,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1531000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1462200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1610200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1431600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1414300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1444500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1446700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1409400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1373800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1359700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1393900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1461400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1453100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1132900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1151900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1270900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1979000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1349000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1515400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1474900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1390000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1293300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1316400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1169200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1136000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1116000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1162900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1227700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1253300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1151400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1224700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1162400</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5987,8 +6147,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6085,8 +6246,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6183,8 +6347,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6281,8 +6448,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6379,106 +6549,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1063100</v>
+      </c>
+      <c r="E72" s="3">
         <v>1040300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1026600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>942800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>882600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>855100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>838300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>784300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>747100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>748400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>798500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>769800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>797700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>800600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>867800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>833800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>796800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>829700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>840900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>816700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>786800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>772500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>784500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>756700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>726800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>709600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>674200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>652300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>608600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>600500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>588900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>537900</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6575,8 +6751,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6673,8 +6852,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6771,106 +6953,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1080600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1054700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1053900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>964000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>897400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>868800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>858600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>797000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>758300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>758500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>810800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>780400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>810000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>811300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>913100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>873700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>833900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>868600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>880200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>853400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>821200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>804200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>816900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>783200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>747000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>725000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>689600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>671600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>622700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>615100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>613700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>557300</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6967,209 +7155,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45409</v>
+      </c>
+      <c r="E80" s="2">
         <v>45318</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45227</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45136</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45045</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44954</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44863</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44772</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44590</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44499</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44317</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44226</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44128</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44037</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43946</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43855</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43764</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43673</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43582</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43491</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43400</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43309</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43218</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43127</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43036</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42945</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42854</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42763</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42672</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E81" s="3">
         <v>23400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>83700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>60200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>51500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>24800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>54000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>43900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>28700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>33900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>37000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-32400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>24200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>29900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>14300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-12100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>27800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>29900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>17200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>40100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>28800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>43700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>38800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>23700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>51100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7204,106 +7401,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E83" s="3">
         <v>45300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>42500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>38000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>37300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>36700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>35500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>35300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>36600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>37300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>37800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>38500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>39100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>43600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>42300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>44100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>45900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>46600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>47400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>47200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>46300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>45900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>45500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>44800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>43400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>42400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>42700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>40200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>37400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>35700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>34500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7400,8 +7601,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7498,8 +7702,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7596,8 +7803,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7694,8 +7904,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7792,106 +8005,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-37400</v>
+      </c>
+      <c r="E89" s="3">
         <v>325100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-37300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>56300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-85100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>246200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-64900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>145500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>104300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>17300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>41500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>102400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>111900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>82300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>85200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>191800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-24000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-53600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-56100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>142800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-55500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>12600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>24600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>103700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>56800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>149900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>42300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>105800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-41600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>182500</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7926,106 +8145,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-42000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-57400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-67200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-51000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-42900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-65200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-54800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-42500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-38400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-43600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-45100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-36700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-31600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-21900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-20700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-18700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-17900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-38200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-45800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-37200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-47300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-31800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-58300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-40100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-47300</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8122,8 +8345,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8220,106 +8446,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-52700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-179900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-40000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-33600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-62600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-49200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-39100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-33000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-43400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-44100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-35500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-28600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-20400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-18300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-15800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-14500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-32500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-38400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-33800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-42600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-39100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-45800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-78400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-32900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-38200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-151600</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8354,8 +8586,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8452,8 +8685,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8550,8 +8786,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8648,8 +8887,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8746,106 +8988,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-187000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>149500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-34100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-24700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-27200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-55100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-58400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-50400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>305900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-85500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-119000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-701200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>522300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-133200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>37800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>65100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>95700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-22800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>25900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-65100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>67700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-16500</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8942,102 +9190,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-74900</v>
+      </c>
+      <c r="E102" s="3">
         <v>85400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-67700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-152800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>158900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-55000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-65300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-125200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>47100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-68700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>318800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-621300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>589100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>42700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-21000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-95300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>105800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-33400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-26100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>59500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>19300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>7800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-12100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>14500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>DY</t>
   </si>
@@ -656,455 +656,468 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45500</v>
+      </c>
+      <c r="E7" s="2">
         <v>45409</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45318</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45227</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45136</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45045</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44954</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44863</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44772</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44590</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44499</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44317</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44226</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44128</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44037</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43946</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43855</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43764</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43673</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43582</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43491</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43400</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43309</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43218</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43127</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43036</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42945</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42854</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42763</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42672</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1203100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1142400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>952500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1136100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1041500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1045500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>917500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1042400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>972300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>876300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>761500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>854000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>787600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>727500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>750700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>810300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>823900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>814300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>737600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>884100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>884200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>833700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>748600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>848200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>799500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>731400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>655100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>756200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>780200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>786300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>701100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>799200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>789200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>952900</v>
+      </c>
+      <c r="E9" s="3">
         <v>921600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>791400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>886700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>830400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>853400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>765700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>850900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>798000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>745700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>656600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>705900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>651400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>620000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>645500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>658400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>658000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>680200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>633200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>724400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>720400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>701800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>633300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>687200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>642400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>599600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>540600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>600800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>606900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>621500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>561400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>615000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>605900</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>250200</v>
+      </c>
+      <c r="E10" s="3">
         <v>220800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>161100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>249400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>211100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>192100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>151800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>191500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>174300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>130600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>104900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>148100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>136200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>107500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>105200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>151900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>165900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>134100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>104400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>159700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>163800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>131900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>115300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>161000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>157100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>131800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>114500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>155400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>173300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>164800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>139700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>184200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>183300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1140,8 +1153,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1241,8 +1255,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,19 +1359,22 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1362,14 +1382,14 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1377,32 +1397,32 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>40800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>100</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1416,8 +1436,8 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1431,121 +1451,127 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>46600</v>
+      </c>
+      <c r="E15" s="3">
         <v>45200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>45300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>42500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>38000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>37300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>36700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>35500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>35300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>36600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>37300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>37800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>38500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>39100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>43600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>42300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>44100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>45900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>46600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>47400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>47200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>46300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>45900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>45500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>44800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>43400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>42400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>42700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>40200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>37400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>35700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>34500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,210 +1604,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1100000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1061400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>909700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1016700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>953200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>973000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>874400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>965100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>906700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>851700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>757800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>810500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>754600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>726200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>753000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>763300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>769900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>832700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>740900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>841600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>832700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>806700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>752700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>801500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>751700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>705200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>643400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>708100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>706700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>720200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>655300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>709700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>704100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>103100</v>
+      </c>
+      <c r="E18" s="3">
         <v>81000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>42800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>119400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>88300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>72500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>43100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>77300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>65600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>43500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>33000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>47000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>54000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-18400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>42500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>51500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>27000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>46700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>47800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>26200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>48100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>73500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>66100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>45800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>89500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,513 +1850,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E20" s="3">
         <v>9300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>6900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>5000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>5700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>7700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>6000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>4800</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>1000</v>
       </c>
       <c r="AH20" s="3">
         <v>1000</v>
       </c>
       <c r="AI20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E21" s="3">
         <v>135500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>92100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>168800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>132000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>114700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>80200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>115200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>103500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>66000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>41200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>81800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>72500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>43100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>42000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>93000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>101300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>28600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>43900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>91300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>102700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>79100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>43000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>95100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>96700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>77200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>54400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>96700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>119800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>108300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>82600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>125000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>124700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E22" s="3">
         <v>12800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>9300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5900</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>4700</v>
       </c>
       <c r="R22" s="3">
         <v>4700</v>
       </c>
       <c r="S22" s="3">
+        <v>4700</v>
+      </c>
+      <c r="T22" s="3">
         <v>7900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>12400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>11300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9900</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>9700</v>
       </c>
       <c r="AE22" s="3">
         <v>9700</v>
       </c>
       <c r="AF22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AG22" s="3">
         <v>9400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>9100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>94800</v>
+      </c>
+      <c r="E23" s="3">
         <v>77400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>31800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>112400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>81800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>66100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>31900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>69200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>58900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>20200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>34900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>24700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-6300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>46000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>49300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-29700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-15300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>30800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>42600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>20500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-15400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>38300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>41400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>23700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>44400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>69800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>61500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>37700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>81400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E24" s="3">
         <v>14900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>28600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>21500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-5700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>12000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>12200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-5200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>12700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>10500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>11500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>15600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>26100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>22800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>14000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>30300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>29600</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,210 +2472,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E26" s="3">
         <v>62600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>23400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>83700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>60200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>51500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>24800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>54000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>43900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>28700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>18200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>33900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>37000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-32400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>24200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>29900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>14300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-12100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>27800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>29900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>17200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>28800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>43700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>38800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>23700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>51100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E27" s="3">
         <v>62600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>23400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>83700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>60200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>51500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>24800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>54000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>43900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>28700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>33900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>37000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-32400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>24200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>29900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>14300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-12100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>27800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>29900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>17200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>28800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>43700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>38800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>23700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>51100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,8 +2784,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2752,8 +2813,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -2770,11 +2831,11 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3">
         <v>2600</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2782,11 +2843,11 @@
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3">
         <v>-1100</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2794,11 +2855,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2806,11 +2867,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>32200</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2827,8 +2888,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +2992,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,210 +3096,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-6900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-5000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AH32" s="3">
         <v>-1000</v>
       </c>
       <c r="AI32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E33" s="3">
         <v>62600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>23400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>83700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>60200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>51500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>24800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>54000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>43900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>28700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>33900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>37000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-32400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-11200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>24200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>29900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>14300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-12100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>27800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>29900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>17200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>40100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>28800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>43700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>38800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>23700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>51100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,215 +3408,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E35" s="3">
         <v>62600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>23400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>83700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>60200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>51500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>24800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>54000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>43900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>28700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>33900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>37000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-32400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-11200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>24200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>29900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>14300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-12100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>27800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>29900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>17200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>40100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>28800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>43700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>38800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>23700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>51100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45500</v>
+      </c>
+      <c r="E38" s="2">
         <v>45409</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45318</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45227</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45136</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45045</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44954</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44863</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44772</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44590</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44499</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44317</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44226</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44128</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44037</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43946</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43855</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43764</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43673</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43582</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43491</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43400</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43309</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43218</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43127</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43036</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42945</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42854</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42763</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42672</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3661,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,109 +3699,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E41" s="3">
         <v>26100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>101100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>83400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>71400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>224200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>65300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>120300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>185600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>310800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>263700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>261900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>330600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>22500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>643900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>54600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>33600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>128300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>21500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>23900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>57900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>84000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>24500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>38600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>19400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>29500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>21700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3815,486 +3905,501 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1588000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1442300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1298700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1534900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1303300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1242800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1114900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1297800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1170700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1043300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>933200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1077900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1102800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1048500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1057000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1144300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1156600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1145800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1073600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1262900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1156800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1001900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>844600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1003300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>863500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>763100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>332600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>349600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>377300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>355100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>335500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>329800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>101200</v>
+      </c>
+      <c r="E44" s="3">
         <v>104000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>108600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>114000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>117200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>115700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>115000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>107100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>98900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>94100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>81300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>69900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>69700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>71100</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>70800</v>
       </c>
       <c r="R44" s="3">
         <v>70800</v>
       </c>
       <c r="S44" s="3">
+        <v>70800</v>
+      </c>
+      <c r="T44" s="3">
         <v>77800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>92600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>98300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>104900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>107400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>105200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>94400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>90800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>87800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>84300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>448500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>490400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>472500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>529100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>481600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>570000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>450600</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E45" s="3">
         <v>54400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>41700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>44100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>51300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>53900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>38600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>42800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>43900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>47000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>30900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>37500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>43300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>47900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>29000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>38400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>49700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>48600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>31800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>32300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>31100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>37800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>29100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>33300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>30100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>30800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>39700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>28800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>50100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>46700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>41700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>45400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1760700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1626800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1550000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1708700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1555200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1483800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1492700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1513000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1433800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1370000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1356100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1449000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1477700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1498100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1168600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1265500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1306600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1930900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1258300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1411900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1307800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1178500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1096400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1148900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1005300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>936100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>904800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>893400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>938500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>950200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>888300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>966900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>851200</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
         <v>1100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>5300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>14100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>15300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>16700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>16200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>17600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>18600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>19900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>21300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>22700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>24200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>26200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>28400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>55200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>32000</v>
-      </c>
-      <c r="AA47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>8</v>
@@ -4320,210 +4425,219 @@
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>563000</v>
+      </c>
+      <c r="E48" s="3">
         <v>538700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>521300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>505100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>466000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>447100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>435100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>403300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>377600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>361100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>355900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>346200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>343600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>340500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>337100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>354200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>385500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>422100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>446200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>463000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>491700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>498400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>424800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>428300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>423700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>416300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>414800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>423300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>422100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>378400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>344100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>337700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>429500</v>
+      </c>
+      <c r="E49" s="3">
         <v>423800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>420900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>425700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>352100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>355600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>359100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>362600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>366500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>370400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>374300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>378300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>382500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>387100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>391800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>397000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>402000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>407200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>465700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>470900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>476200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>481500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>486900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>492300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>498100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>503900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>493200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>499100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>505300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>513100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>498200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>500300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>508000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4737,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,109 +4841,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E52" s="3">
         <v>21300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>20800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>18400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>18000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>18100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>21400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>21100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>29700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>30600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>31400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>24800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>25500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>26400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>24400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>34200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>31700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>25400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>26800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>28200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>36800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>33400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>34300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>35800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>33500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,109 +5049,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2779400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2611600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2516900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2664200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2395600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2311700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2313300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2305300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2206400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2132100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2118200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2204700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2241900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2263000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1944200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2065100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2144700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2812900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2217600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2395600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2328400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2211200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2097500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2133200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1952400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1883000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1841000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1852500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1899300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1876000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1766400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1838400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1719700</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5193,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,114 +5231,118 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>233500</v>
+      </c>
+      <c r="E57" s="3">
         <v>212900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>222100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>215300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>204800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>196200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>207700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>201000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>187600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>176400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>155900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>173600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>173200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>171000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>159000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>183700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>177300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>194400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>119600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>129500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>140300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>138700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>119500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>134700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>125700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>112200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>92400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>109900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>133000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>119300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>99300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>114700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>115500</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>17500</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>17500</v>
@@ -5238,22 +5372,22 @@
         <v>17500</v>
       </c>
       <c r="N58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="O58" s="3">
         <v>13100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>66600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>61500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>81700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>78100</v>
-      </c>
-      <c r="S58" s="3">
-        <v>22500</v>
       </c>
       <c r="T58" s="3">
         <v>22500</v>
@@ -5265,450 +5399,465 @@
         <v>22500</v>
       </c>
       <c r="W58" s="3">
+        <v>22500</v>
+      </c>
+      <c r="X58" s="3">
         <v>16900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>11300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5600</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>31300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>28900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>26500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>24100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>21700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>14400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>18800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>17500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>277600</v>
+      </c>
+      <c r="E59" s="3">
         <v>283200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>266700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>256000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>237200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>219400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>244300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>252600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>227100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>201700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>208400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>206400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>207600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>203500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>207800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>201900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>211500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>211400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>180900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>212800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>199800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>191700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>159900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>169300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>153300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>134800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>140800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>149200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>163900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>155100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>145000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>179700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>511100</v>
+      </c>
+      <c r="E60" s="3">
         <v>513600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>506300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>488800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>459400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>433100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>469600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>471100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>432100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>395700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>381800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>393200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>447500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>436100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>448500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>463700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>411300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>428300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>323000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>364800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>357000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>341700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>285000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>304000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>310300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>275900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>259600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>283100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>318500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>288900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>263200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>312000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>322600</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>942400</v>
+      </c>
+      <c r="E61" s="3">
         <v>842400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>791400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>949400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>799400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>803400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>807400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>811400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>815300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>819300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>823300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>827200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>831200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>835200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>501600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>490000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>665500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1363900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>844400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>970200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>932300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>867400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>867600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>867800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>727300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>731700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>733800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>736000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>738300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>811600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>740600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>774500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>706200</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>167500</v>
+      </c>
+      <c r="E62" s="3">
         <v>175000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>164500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>172000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>172700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>177800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>167600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>164200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>161900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>158800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>154600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>173500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>182700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>181800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>182800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>198200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>194100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>186800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>181600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>180400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>185700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>181000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>140800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>144500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>131500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>128400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>122500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>143800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>170900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>152800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>147600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>138200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +5957,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6061,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,109 +6165,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1620900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1531000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1462200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1610200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1431600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1414300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1444500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1446700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1409400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1373800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1359700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1393900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1461400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1453100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1132900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1151900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1270900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1979000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1349000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1515400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1474900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1390000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1293300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1316400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1169200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1136000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1116000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1162900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1227700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1253300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1151400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1224700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1162400</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6309,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6411,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6515,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6451,8 +6619,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,109 +6723,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1131500</v>
+      </c>
+      <c r="E72" s="3">
         <v>1063100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1040300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1026600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>942800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>882600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>855100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>838300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>784300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>747100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>748400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>798500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>769800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>797700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>800600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>867800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>833800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>796800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>829700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>840900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>816700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>786800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>772500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>784500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>756700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>726800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>709600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>674200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>652300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>608600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>600500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>588900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>537900</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +6931,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7035,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,109 +7139,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1158400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1080600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1054700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1053900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>964000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>897400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>868800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>858600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>797000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>758300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>758500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>810800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>780400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>810000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>811300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>913100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>873700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>833900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>868600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>880200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>853400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>821200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>804200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>816900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>783200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>747000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>725000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>689600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>671600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>622700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>615100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>613700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>557300</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,215 +7347,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45500</v>
+      </c>
+      <c r="E80" s="2">
         <v>45409</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45318</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45227</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45136</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45045</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44954</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44863</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44772</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44590</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44499</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44317</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44226</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44128</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44037</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43946</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43855</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43764</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43673</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43582</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43491</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43400</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43309</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43218</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43127</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43036</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42945</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42854</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42763</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42672</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>68400</v>
+      </c>
+      <c r="E81" s="3">
         <v>62600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>23400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>83700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>60200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>51500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>24800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>54000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>43900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>28700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>33900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>37000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-32400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-11200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>24200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>29900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>14300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-12100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>27800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>29900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>17200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>40100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>28800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>43700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>38800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>23700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>51100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,109 +7600,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>46600</v>
+      </c>
+      <c r="E83" s="3">
         <v>45200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>45300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>42500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>38000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>37300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>36700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>35500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>35300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>36600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>37300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>37800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>38500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>39100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>43600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>42300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>44100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>45900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>46600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>47400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>47200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>46300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>45900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>45500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>44800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>43400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>42400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>42700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>40200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>37400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>35700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>34500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +7806,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +7910,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8014,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8118,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,109 +8222,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-37400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>325100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-37300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>56300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-85100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>246200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-64900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>145500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>104300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>41500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>102400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>111900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>82300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>85200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>191800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-24000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-53600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-56100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>142800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-55500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>12600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>24600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>103700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>56800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>149900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>42300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>105800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-41600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>182500</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,109 +8366,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-65400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-42000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-57400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-67200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-51000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-42900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-65200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-54800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-42500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-38400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-43600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-45100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-36700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-31600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-21900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-20700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-18700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-17900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-38200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-45800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-37200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-47300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-31800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-58300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-40100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-47300</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8572,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,109 +8676,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-76700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-42200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-52700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-179900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-40000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-33600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-62600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-49200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-39100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-33000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-43400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-44100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-35500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-28600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-20400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-18300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-15800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-14500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-32500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-38400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-33800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-39100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-45800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-78400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-32900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-38200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-151600</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,8 +8820,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8688,8 +8922,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9026,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9130,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,109 +9234,115 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>77700</v>
+      </c>
+      <c r="E100" s="3">
         <v>4700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-187000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>149500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-34100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-24700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-27200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-55100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-58400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-50400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>305900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-85500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-119000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-701200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>522300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-133200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>37800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>65100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>95700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-22800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>25900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-65100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>67700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-16500</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9193,105 +9442,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-74900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>85400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-67700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-152800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>158900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-55000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-65300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-125200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>47100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-68700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>318800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-621300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>589100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>42700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-21000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-95300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>105800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-33400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-26100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>59500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>19300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>7800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-12100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>14500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
   <si>
     <t>DY</t>
   </si>
@@ -656,468 +656,481 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45591</v>
+      </c>
+      <c r="E7" s="2">
         <v>45500</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45409</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45318</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45136</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45045</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44954</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44863</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44772</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44590</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44499</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44317</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44226</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44128</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44037</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43946</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43855</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43764</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43673</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43582</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43491</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43400</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43309</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43218</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43127</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43036</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42945</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42854</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42763</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42672</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1272000</v>
+      </c>
+      <c r="E8" s="3">
         <v>1203100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1142400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>952500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1136100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1041500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1045500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>917500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1042400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>972300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>876300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>761500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>854000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>787600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>727500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>750700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>810300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>823900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>814300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>737600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>884100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>884200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>833700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>748600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>848200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>799500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>731400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>655100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>756200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>780200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>786300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>701100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>799200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>789200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1007400</v>
+      </c>
+      <c r="E9" s="3">
         <v>952900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>921600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>791400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>886700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>830400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>853400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>765700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>850900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>798000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>745700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>656600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>705900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>651400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>620000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>645500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>658400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>658000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>680200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>633200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>724400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>720400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>701800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>633300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>687200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>642400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>599600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>540600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>600800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>606900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>621500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>561400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>615000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>605900</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>264600</v>
+      </c>
+      <c r="E10" s="3">
         <v>250200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>220800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>161100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>249400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>211100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>192100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>151800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>191500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>174300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>130600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>104900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>148100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>136200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>107500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>105200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>151900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>165900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>134100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>104400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>159700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>163800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>131900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>115300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>161000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>157100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>131800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>114500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>155400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>173300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>164800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>139700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>184200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>183300</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1154,8 +1167,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1258,8 +1272,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1362,37 +1379,40 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+        <v>-4000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-7200</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+        <v>-12400</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-7600</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+        <v>-7800</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1400,33 +1420,33 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>40800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1439,8 +1459,8 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1454,124 +1474,130 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E15" s="3">
         <v>46600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>45200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>45300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>42500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>38000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>37300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>36700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>35500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>35300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>36600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>37300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>37800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>38500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>39100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>43600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>42300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>44100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>45900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>46600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>47400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>47200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>46300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>45900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>45500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>44800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>43400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>42400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>42700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>40200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>37400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>35700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>34500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1605,216 +1631,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1100000</v>
+        <v>1166000</v>
       </c>
       <c r="E17" s="3">
+        <v>1099000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1061400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>909700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1016700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>953200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>973000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>874400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>965100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>906700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>851700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>757800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>810500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>754600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>726200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>753000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>763300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>769900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>832700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>740900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>841600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>832700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>806700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>752700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>801500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>751700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>705200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>643400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>708100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>706700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>720200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>655300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>709700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>704100</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>103100</v>
+        <v>106000</v>
       </c>
       <c r="E18" s="3">
+        <v>104000</v>
+      </c>
+      <c r="F18" s="3">
         <v>81000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>42800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>119400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>88300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>72500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>43100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>77300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>65600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>43500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>33000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>47000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>54000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-18400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>42500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>51500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>27000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>46700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>47800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>26200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>11700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>48100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>73500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>66100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>45800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>89500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1851,528 +1884,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6400</v>
+        <v>1300</v>
       </c>
       <c r="E20" s="3">
-        <v>9300</v>
+        <v>1700</v>
       </c>
       <c r="F20" s="3">
-        <v>3900</v>
+        <v>3200</v>
       </c>
       <c r="G20" s="3">
-        <v>6900</v>
+        <v>600</v>
       </c>
       <c r="H20" s="3">
-        <v>5800</v>
+        <v>1500</v>
       </c>
       <c r="I20" s="3">
-        <v>5000</v>
+        <v>1800</v>
       </c>
       <c r="J20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>7700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>6000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>4800</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>1000</v>
       </c>
       <c r="AI20" s="3">
         <v>1000</v>
       </c>
       <c r="AJ20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AK20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>156000</v>
+        <v>156700</v>
       </c>
       <c r="E21" s="3">
-        <v>135500</v>
+        <v>148900</v>
       </c>
       <c r="F21" s="3">
-        <v>92100</v>
+        <v>123100</v>
       </c>
       <c r="G21" s="3">
-        <v>168800</v>
+        <v>87500</v>
       </c>
       <c r="H21" s="3">
-        <v>132000</v>
+        <v>160500</v>
       </c>
       <c r="I21" s="3">
-        <v>114700</v>
+        <v>124500</v>
       </c>
       <c r="J21" s="3">
+        <v>106900</v>
+      </c>
+      <c r="K21" s="3">
         <v>80200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>115200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>103500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>66000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>41200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>81800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>72500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>43100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>42000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>93000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>101300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>28600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>43900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>91300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>102700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>79100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>43000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>95100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>96700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>77200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>54400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>96700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>119800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>108300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>82600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>125000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>124700</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E22" s="3">
         <v>14700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>12300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>9100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>5900</v>
-      </c>
-      <c r="R22" s="3">
-        <v>4700</v>
       </c>
       <c r="S22" s="3">
         <v>4700</v>
       </c>
       <c r="T22" s="3">
+        <v>4700</v>
+      </c>
+      <c r="U22" s="3">
         <v>7900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>13100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>12200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>12400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>11300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>10200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9900</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>9700</v>
       </c>
       <c r="AF22" s="3">
         <v>9700</v>
       </c>
       <c r="AG22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AH22" s="3">
         <v>9400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>9200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E23" s="3">
         <v>94800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>77400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>31800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>112400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>81800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>66100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>31900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>69200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>58900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>20200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>34900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>24700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-6300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>46000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>49300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-29700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-15300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>30800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>42600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>20500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>38300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>41400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>23700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>44400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>69800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>61500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>37700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>81400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E24" s="3">
         <v>26400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>28600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-5700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>12000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>12200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-5200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>12700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>10500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>11500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>15600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>26100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>22800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>14000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>30300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>29600</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2475,216 +2524,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E26" s="3">
         <v>68400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>62600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>23400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>83700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>60200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>51500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>24800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>54000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>43900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>28700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>18200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>33900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>37000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-32400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>24200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>29900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>14300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-12100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>27800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>29900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>17200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>28800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>43700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>38800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>23700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>51100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E27" s="3">
         <v>68400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>62600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>23400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>83700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>60200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>51500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>24800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>54000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>43900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>28700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>33900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>37000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-32400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>24200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>29900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>14300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-12100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>27800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>29900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>17200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>28800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>43700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>38800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>23700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>51100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2787,8 +2845,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2816,8 +2877,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -2834,35 +2895,35 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3">
         <v>2600</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
         <v>-1100</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2870,12 +2931,12 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>32200</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2891,8 +2952,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2995,8 +3059,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3099,216 +3166,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6400</v>
+        <v>-1300</v>
       </c>
       <c r="E32" s="3">
-        <v>-9300</v>
+        <v>-1700</v>
       </c>
       <c r="F32" s="3">
-        <v>-3900</v>
+        <v>-3200</v>
       </c>
       <c r="G32" s="3">
-        <v>-6900</v>
+        <v>-600</v>
       </c>
       <c r="H32" s="3">
-        <v>-5800</v>
+        <v>-1500</v>
       </c>
       <c r="I32" s="3">
-        <v>-5000</v>
+        <v>-1800</v>
       </c>
       <c r="J32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AI32" s="3">
         <v>-1000</v>
       </c>
       <c r="AJ32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E33" s="3">
         <v>68400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>62600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>23400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>83700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>60200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>51500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>24800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>54000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>43900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>28700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>33900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>37000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-32400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-11200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>24200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>29900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>14300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-12100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>27800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>29900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>17200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>40100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>28800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>43700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>38800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>23700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>51100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3411,221 +3487,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E35" s="3">
         <v>68400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>62600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>23400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>83700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>60200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>51500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>24800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>54000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>43900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>28700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>33900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>37000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-32400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-11200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>24200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>29900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>14300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-12100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>27800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>29900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>17200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>40100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>28800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>43700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>38800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>23700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>51100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45591</v>
+      </c>
+      <c r="E38" s="2">
         <v>45500</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45409</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45318</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45136</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45045</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44954</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44863</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44772</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44590</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44499</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44317</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44226</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44128</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44037</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43946</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43855</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43764</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43673</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43582</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43491</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43400</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43309</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43218</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43127</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43036</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42945</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42854</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42763</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42672</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3662,8 +3747,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3700,135 +3786,139 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E41" s="3">
         <v>19600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>26100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>101100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>83400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>71400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>224200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>65300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>120300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>185600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>310800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>263700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>261900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>330600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>22500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>643900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>54600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>33600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>128300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>21500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>23900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>57900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>84000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>24500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>38600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>19400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>29500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>21700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>15200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>22300</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>20200</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>22300</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3908,502 +3998,517 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1723700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1588000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1442300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1298700</v>
       </c>
-      <c r="G43" s="3">
-        <v>1534900</v>
-      </c>
       <c r="H43" s="3">
-        <v>1303300</v>
+        <v>1535000</v>
       </c>
       <c r="I43" s="3">
-        <v>1242800</v>
+        <v>1303400</v>
       </c>
       <c r="J43" s="3">
+        <v>1243600</v>
+      </c>
+      <c r="K43" s="3">
         <v>1114900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1297800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1170700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1043300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>933200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1077900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1102800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1048500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1057000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1144300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1156600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1145800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1073600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1262900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1156800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1001900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>844600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1003300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>863500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>763100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>332600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>349600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>377300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>355100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>335500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>329800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E44" s="3">
         <v>101200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>104000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>108600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>114000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>117200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>115700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>115000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>107100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>98900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>94100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>81300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>69900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>69700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>71100</v>
-      </c>
-      <c r="R44" s="3">
-        <v>70800</v>
       </c>
       <c r="S44" s="3">
         <v>70800</v>
       </c>
       <c r="T44" s="3">
+        <v>70800</v>
+      </c>
+      <c r="U44" s="3">
         <v>77800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>92600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>98300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>104900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>107400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>105200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>94400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>90800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>87800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>84300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>448500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>490400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>472500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>529100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>481600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>570000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>450600</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>51900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>54400</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
+        <v>38600</v>
+      </c>
+      <c r="L45" s="3">
+        <v>42800</v>
+      </c>
+      <c r="M45" s="3">
+        <v>43900</v>
+      </c>
+      <c r="N45" s="3">
+        <v>47000</v>
+      </c>
+      <c r="O45" s="3">
+        <v>30900</v>
+      </c>
+      <c r="P45" s="3">
+        <v>37500</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>43300</v>
+      </c>
+      <c r="R45" s="3">
+        <v>47900</v>
+      </c>
+      <c r="S45" s="3">
+        <v>29000</v>
+      </c>
+      <c r="T45" s="3">
+        <v>38400</v>
+      </c>
+      <c r="U45" s="3">
+        <v>49700</v>
+      </c>
+      <c r="V45" s="3">
+        <v>48600</v>
+      </c>
+      <c r="W45" s="3">
+        <v>31800</v>
+      </c>
+      <c r="X45" s="3">
+        <v>32300</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>31100</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>37800</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>29100</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>33300</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>30800</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>39700</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>28800</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>50100</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>46700</v>
+      </c>
+      <c r="AI45" s="3">
         <v>41700</v>
       </c>
-      <c r="G45" s="3">
-        <v>44100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>51300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>53900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>38600</v>
-      </c>
-      <c r="K45" s="3">
-        <v>42800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>43900</v>
-      </c>
-      <c r="M45" s="3">
-        <v>47000</v>
-      </c>
-      <c r="N45" s="3">
-        <v>30900</v>
-      </c>
-      <c r="O45" s="3">
-        <v>37500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>43300</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>47900</v>
-      </c>
-      <c r="R45" s="3">
-        <v>29000</v>
-      </c>
-      <c r="S45" s="3">
-        <v>38400</v>
-      </c>
-      <c r="T45" s="3">
-        <v>49700</v>
-      </c>
-      <c r="U45" s="3">
-        <v>48600</v>
-      </c>
-      <c r="V45" s="3">
-        <v>31800</v>
-      </c>
-      <c r="W45" s="3">
-        <v>32300</v>
-      </c>
-      <c r="X45" s="3">
-        <v>31100</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>37800</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>29100</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>33300</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>30100</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>30800</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>39700</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>28800</v>
-      </c>
-      <c r="AF45" s="3">
-        <v>50100</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>46700</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>41700</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>45400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1896800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1760700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1626800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1550000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1708700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1555200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1483800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1492700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1513000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1433800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1370000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1356100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1449000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1477700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1498100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1168600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1265500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1306600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1930900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1258300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1411900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1307800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1178500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1096400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1148900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1005300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>936100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>904800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>893400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>938500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>950200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>888300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>966900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>851200</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G47" s="3">
-        <v>3800</v>
-      </c>
-      <c r="H47" s="3">
-        <v>5300</v>
-      </c>
-      <c r="I47" s="3">
-        <v>6800</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>8300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>12500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>15300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>16700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>16200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>17600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>18600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>19900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>21300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>22700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>24200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>26200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>28400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>55200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>32000</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4428,216 +4533,225 @@
       <c r="AJ47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>622800</v>
+      </c>
+      <c r="E48" s="3">
         <v>563000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>538700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>521300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>505100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>466000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>447100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>435100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>403300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>377600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>361100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>355900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>346200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>343600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>340500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>337100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>354200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>385500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>422100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>446200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>463000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>491700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>498400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>424800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>428300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>423700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>416300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>414800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>423300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>422100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>378400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>344100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>337700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>560000</v>
+      </c>
+      <c r="E49" s="3">
         <v>429500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>423800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>420900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>425700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>352100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>355600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>359100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>362600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>366500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>370400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>374300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>378300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>382500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>387100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>391800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>397000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>402000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>407200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>465700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>470900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>476200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>481500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>486900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>492300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>498100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>503900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>493200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>499100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>505300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>513100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>498200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>500300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>508000</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4740,8 +4854,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4844,112 +4961,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>26200</v>
+        <v>29800</v>
       </c>
       <c r="E52" s="3">
-        <v>21300</v>
+        <v>20700</v>
       </c>
       <c r="F52" s="3">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="G52" s="3">
-        <v>20800</v>
+        <v>19500</v>
       </c>
       <c r="H52" s="3">
-        <v>16900</v>
+        <v>17900</v>
       </c>
       <c r="I52" s="3">
-        <v>18400</v>
+        <v>13900</v>
       </c>
       <c r="J52" s="3">
+        <v>15000</v>
+      </c>
+      <c r="K52" s="3">
         <v>18000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>18100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>21400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>21100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>29000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>29700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>30600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>31400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>24800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>25500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>26400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>24400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>34200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>31700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>25400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>26800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>28200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>36800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>33400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>34300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>35800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>33500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5052,112 +5175,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3114700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2779400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2611600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2516900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2664200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2395600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2311700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2313300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2305300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2206400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2132100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2118200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2204700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2241900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2263000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1944200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2065100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2144700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2812900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2217600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2395600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2328400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2211200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2097500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2133200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1952400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1883000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1841000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1852500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1899300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1876000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1766400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1838400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1719700</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5194,8 +5323,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5232,135 +5362,139 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>241000</v>
+      </c>
+      <c r="E57" s="3">
         <v>233500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>212900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>222100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>215300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>204800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>196200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>207700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>201000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>187600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>176400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>155900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>173600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>173200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>171000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>159000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>183700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>177300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>194400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>119600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>129500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>140300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>138700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>119500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>134700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>125700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>112200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>92400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>109900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>133000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>119300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>99300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>114700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>115500</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>39800</v>
       </c>
       <c r="E58" s="3">
-        <v>17500</v>
+        <v>33300</v>
       </c>
       <c r="F58" s="3">
-        <v>17500</v>
+        <v>50400</v>
       </c>
       <c r="G58" s="3">
-        <v>17500</v>
+        <v>49500</v>
       </c>
       <c r="H58" s="3">
-        <v>17500</v>
+        <v>47600</v>
       </c>
       <c r="I58" s="3">
-        <v>17500</v>
+        <v>46800</v>
       </c>
       <c r="J58" s="3">
-        <v>17500</v>
+        <v>46100</v>
       </c>
       <c r="K58" s="3">
         <v>17500</v>
@@ -5375,22 +5509,22 @@
         <v>17500</v>
       </c>
       <c r="O58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="P58" s="3">
         <v>13100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>66600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>61500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>81700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>78100</v>
-      </c>
-      <c r="T58" s="3">
-        <v>22500</v>
       </c>
       <c r="U58" s="3">
         <v>22500</v>
@@ -5402,462 +5536,477 @@
         <v>22500</v>
       </c>
       <c r="X58" s="3">
+        <v>22500</v>
+      </c>
+      <c r="Y58" s="3">
         <v>16900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>11300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5600</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
       <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
         <v>31300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>28900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>26500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>24100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>21700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>14400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>18800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>17500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>277600</v>
+        <v>136900</v>
       </c>
       <c r="E59" s="3">
-        <v>283200</v>
+        <v>67600</v>
       </c>
       <c r="F59" s="3">
-        <v>266700</v>
+        <v>103600</v>
       </c>
       <c r="G59" s="3">
-        <v>256000</v>
+        <v>73700</v>
       </c>
       <c r="H59" s="3">
-        <v>237200</v>
+        <v>61700</v>
       </c>
       <c r="I59" s="3">
-        <v>219400</v>
+        <v>57400</v>
       </c>
       <c r="J59" s="3">
+        <v>68100</v>
+      </c>
+      <c r="K59" s="3">
         <v>244300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>252600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>227100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>201700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>208400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>206400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>207600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>203500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>207800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>201900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>211500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>211400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>180900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>212800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>199800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>191700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>159900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>169300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>153300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>134800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>140800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>149200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>163900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>155100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>145000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>179700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>608500</v>
+      </c>
+      <c r="E60" s="3">
         <v>511100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>513600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>506300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>488800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>459400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>433100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>469600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>471100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>432100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>395700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>381800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>393200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>447500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>436100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>448500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>463700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>411300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>428300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>323000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>364800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>357000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>341700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>285000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>304000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>310300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>275900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>259600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>283100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>318500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>288900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>263200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>312000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>322600</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>942400</v>
+        <v>1165700</v>
       </c>
       <c r="E61" s="3">
-        <v>842400</v>
+        <v>988600</v>
       </c>
       <c r="F61" s="3">
-        <v>791400</v>
+        <v>889500</v>
       </c>
       <c r="G61" s="3">
-        <v>949400</v>
+        <v>835500</v>
       </c>
       <c r="H61" s="3">
-        <v>799400</v>
+        <v>993300</v>
       </c>
       <c r="I61" s="3">
-        <v>803400</v>
+        <v>842600</v>
       </c>
       <c r="J61" s="3">
+        <v>846900</v>
+      </c>
+      <c r="K61" s="3">
         <v>807400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>811400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>815300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>819300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>823300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>827200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>831200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>835200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>501600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>490000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>665500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1363900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>844400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>970200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>932300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>867400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>867600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>867800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>727300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>731700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>733800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>736000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>738300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>811600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>740600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>774500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>706200</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>167500</v>
+        <v>75100</v>
       </c>
       <c r="E62" s="3">
-        <v>175000</v>
+        <v>77300</v>
       </c>
       <c r="F62" s="3">
-        <v>164500</v>
+        <v>76200</v>
       </c>
       <c r="G62" s="3">
-        <v>172000</v>
+        <v>70800</v>
       </c>
       <c r="H62" s="3">
-        <v>172700</v>
+        <v>70200</v>
       </c>
       <c r="I62" s="3">
-        <v>177800</v>
+        <v>68300</v>
       </c>
       <c r="J62" s="3">
+        <v>72100</v>
+      </c>
+      <c r="K62" s="3">
         <v>167600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>164200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>161900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>158800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>154600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>173500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>182700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>181800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>182800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>198200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>194100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>186800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>181600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>180400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>185700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>181000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>140800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>144500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>131500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>128400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>122500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>143800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>170900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>152800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>147600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>138200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5960,8 +6109,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6064,8 +6216,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6168,112 +6323,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1881000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1620900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1531000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1462200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1610200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1431600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1414300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1444500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1446700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1409400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1373800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1359700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1393900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1461400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1453100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1132900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1151900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1270900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1979000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1349000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1515400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1474900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1390000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1293300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1316400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1169200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1136000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1116000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1162900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1227700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1253300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1151400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1224700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1162400</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6310,8 +6471,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6414,8 +6576,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6518,8 +6683,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6622,8 +6790,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6726,112 +6897,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1201300</v>
+      </c>
+      <c r="E72" s="3">
         <v>1131500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1063100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1040300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1026600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>942800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>882600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>855100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>838300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>784300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>747100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>748400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>798500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>769800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>797700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>800600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>867800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>833800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>796800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>829700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>840900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>816700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>786800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>772500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>784500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>756700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>726800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>709600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>674200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>652300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>608600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>600500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>588900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>537900</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6934,8 +7111,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7038,8 +7218,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7142,112 +7325,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1233700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1158400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1080600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1054700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1053900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>964000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>897400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>868800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>858600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>797000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>758300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>758500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>810800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>780400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>810000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>811300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>913100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>873700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>833900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>868600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>880200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>853400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>821200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>804200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>816900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>783200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>747000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>725000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>689600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>671600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>622700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>615100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>613700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>557300</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7350,221 +7539,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45591</v>
+      </c>
+      <c r="E80" s="2">
         <v>45500</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45409</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45318</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45136</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45045</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44954</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44863</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44772</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44590</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44499</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44317</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44226</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44128</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44037</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43946</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43855</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43764</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43673</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43582</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43491</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43400</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43309</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43218</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43127</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43036</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42945</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42854</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42763</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42672</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E81" s="3">
         <v>68400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>62600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>23400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>83700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>60200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>51500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>24800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>54000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>43900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>28700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>33900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>37000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-32400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-11200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>24200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>29900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>14300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-12100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>27800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>29900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>17200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>40100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>28800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>43700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>38800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>23700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>51100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7601,112 +7799,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>34500</v>
+      </c>
+      <c r="F83" s="3">
+        <v>33800</v>
+      </c>
+      <c r="G83" s="3">
+        <v>33100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>31600</v>
+      </c>
+      <c r="I83" s="3">
+        <v>31400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>32700</v>
+      </c>
+      <c r="K83" s="3">
+        <v>36700</v>
+      </c>
+      <c r="L83" s="3">
+        <v>35500</v>
+      </c>
+      <c r="M83" s="3">
+        <v>35300</v>
+      </c>
+      <c r="N83" s="3">
+        <v>36600</v>
+      </c>
+      <c r="O83" s="3">
+        <v>37300</v>
+      </c>
+      <c r="P83" s="3">
+        <v>37800</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>38500</v>
+      </c>
+      <c r="R83" s="3">
+        <v>39100</v>
+      </c>
+      <c r="S83" s="3">
+        <v>43600</v>
+      </c>
+      <c r="T83" s="3">
+        <v>42300</v>
+      </c>
+      <c r="U83" s="3">
+        <v>44100</v>
+      </c>
+      <c r="V83" s="3">
+        <v>45900</v>
+      </c>
+      <c r="W83" s="3">
         <v>46600</v>
       </c>
-      <c r="E83" s="3">
-        <v>45200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>45300</v>
-      </c>
-      <c r="G83" s="3">
-        <v>42500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>38000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>37300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>36700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>35500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>35300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>36600</v>
-      </c>
-      <c r="N83" s="3">
-        <v>37300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>37800</v>
-      </c>
-      <c r="P83" s="3">
-        <v>38500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>39100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>43600</v>
-      </c>
-      <c r="S83" s="3">
-        <v>42300</v>
-      </c>
-      <c r="T83" s="3">
-        <v>44100</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="X83" s="3">
+        <v>47400</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>47200</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>46300</v>
+      </c>
+      <c r="AA83" s="3">
         <v>45900</v>
       </c>
-      <c r="V83" s="3">
-        <v>46600</v>
-      </c>
-      <c r="W83" s="3">
-        <v>47400</v>
-      </c>
-      <c r="X83" s="3">
-        <v>47200</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>46300</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>45900</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>45500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>44800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>43400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>42400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>42700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>40200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>37400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>35700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>34500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7809,8 +8011,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7913,8 +8118,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8017,8 +8225,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8121,8 +8332,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8225,112 +8439,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-37400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>325100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-37300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>56300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-85100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>246200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-12000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-64900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>145500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>104300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>17300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>41500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>102400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>111900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>82300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>85200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>191800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-24000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-53600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-56100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>142800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-55500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>12600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>24600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>103700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>56800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>149900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>42300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>105800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-41600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>182500</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8367,112 +8587,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-74600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-65400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-42000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-57400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-67200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-51000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-42900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-65200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-54800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-42500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-38400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-43600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-45100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-36700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-31600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-21900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-20700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-18700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-17900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-38200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-45800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-47300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-31800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-58300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-40100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-47300</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8575,8 +8799,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8679,112 +8906,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-216500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-76700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-42200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-52700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-179900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-40000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-33600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-62600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-49200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-39100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-33000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-43400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-44100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-35500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-28600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-20400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-18300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-15800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-14500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-32500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-38400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-42600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-39100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-45800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-78400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-32900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-38200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-151600</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8821,31 +9054,32 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8925,8 +9159,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9029,8 +9266,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9133,8 +9373,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9237,135 +9480,141 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>146400</v>
+      </c>
+      <c r="E100" s="3">
         <v>77700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-187000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>149500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-34100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-24700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-27200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-55100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-58400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-50400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>305900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-85500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-119000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-701200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>522300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-133200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>37800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>65100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>95700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-22800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>25900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-65100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>67700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-16500</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9445,108 +9694,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-74900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>85400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-67700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-152800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>158900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-55000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-65300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-125200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>47100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-68700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>318800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-10500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-621300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>589100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>42700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-21000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-95300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>105800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-33400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-26100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>59500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>19300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>7800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-12100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>14500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>DY</t>
   </si>
@@ -656,481 +656,494 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45682</v>
+      </c>
+      <c r="E7" s="2">
         <v>45591</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45500</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45409</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45318</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45227</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45136</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45045</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44954</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44863</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44772</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44590</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44499</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44317</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44226</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44128</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44037</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43946</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43855</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43764</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43673</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43582</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43491</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43400</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43309</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43218</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43127</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43036</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42945</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42854</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42672</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1084500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1272000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1203100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1142400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>952500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1136100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1041500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1045500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>917500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1042400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>972300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>876300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>761500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>854000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>787600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>727500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>750700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>810300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>823900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>814300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>737600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>884100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>884200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>833700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>748600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>848200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>799500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>731400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>655100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>756200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>780200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>786300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>701100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>799200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>789200</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>887900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1007400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>952900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>921600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>791400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>886700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>830400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>853400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>765700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>850900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>798000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>745700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>656600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>705900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>651400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>620000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>645500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>658400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>658000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>680200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>633200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>724400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>720400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>701800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>633300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>687200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>642400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>599600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>540600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>600800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>606900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>621500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>561400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>615000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>605900</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>196600</v>
+      </c>
+      <c r="E10" s="3">
         <v>264600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>250200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>220800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>161100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>249400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>211100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>192100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>151800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>191500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>174300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>130600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>104900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>148100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>136200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>107500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>105200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>151900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>165900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>134100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>104400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>159700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>163800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>131900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>115300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>161000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>157100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>131800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>114500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>155400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>173300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>164800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>139700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>184200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>183300</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1168,8 +1181,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1275,8 +1289,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1382,40 +1399,43 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-7200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-12400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-4600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-8400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-7600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-7800</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1423,33 +1443,33 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>40800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1462,8 +1482,8 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1477,127 +1497,133 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E15" s="3">
         <v>52000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>46600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>45200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>45300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>42500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>38000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>37300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>36700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>35500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>35300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>36600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>37300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>37800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>38500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>39100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>43600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>42300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>44100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>45900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>46600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>47400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>47200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>46300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>45900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>45500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>44800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>43400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>42400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>42700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>40200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>37400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>35700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>34500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1632,222 +1658,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1030900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1166000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1099000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1061400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>909700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1016700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>953200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>973000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>874400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>965100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>906700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>851700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>757800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>810500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>754600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>726200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>753000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>763300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>769900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>832700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>740900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>841600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>832700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>806700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>752700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>801500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>751700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>705200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>643400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>708100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>706700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>720200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>655300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>709700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>704100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E18" s="3">
         <v>106000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>104000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>81000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>42800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>119400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>88300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>72500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>43100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>77300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>65600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>24600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>43500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>33000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>47000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>54000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-18400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-3300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>42500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>51500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>27000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>46700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>47800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>26200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>11700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>48100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>73500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>66100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>45800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>89500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1885,543 +1918,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>1300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>6000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>4800</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>1000</v>
       </c>
       <c r="AJ20" s="3">
         <v>1000</v>
       </c>
       <c r="AK20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AL20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>107400</v>
+      </c>
+      <c r="E21" s="3">
         <v>156700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>148900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>123100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>87500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>160500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>124500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>106900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>80200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>115200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>103500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>66000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>41200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>81800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>72500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>43100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>42000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>93000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>101300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>28600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>43900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>91300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>102700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>79100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>43000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>95100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>96700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>77200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>54400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>96700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>119800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>108300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>82600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>125000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>124700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E22" s="3">
         <v>17500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5900</v>
-      </c>
-      <c r="S22" s="3">
-        <v>4700</v>
       </c>
       <c r="T22" s="3">
         <v>4700</v>
       </c>
       <c r="U22" s="3">
+        <v>4700</v>
+      </c>
+      <c r="V22" s="3">
         <v>7900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>13100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>12900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>12200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>12400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>10400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>10200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9900</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>9700</v>
       </c>
       <c r="AG22" s="3">
         <v>9700</v>
       </c>
       <c r="AH22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AI22" s="3">
         <v>9400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>9200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>9100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>44200</v>
+      </c>
+      <c r="E23" s="3">
         <v>91300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>94800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>77400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>31800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>112400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>81800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>66100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>31900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>69200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>58900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>34900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>24700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>46000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>49300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-29700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-15300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>30800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>42600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>20500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>38300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>41400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>23700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>44400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>69800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>61500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>37700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>81400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E24" s="3">
         <v>21500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>26400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>28600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-5700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>12000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>12200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-5200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>12700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>10500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>11500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>15600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>26100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>22800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>14000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>30300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>29600</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2527,222 +2576,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E26" s="3">
         <v>69800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>68400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>62600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>23400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>83700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>60200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>51500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>24800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>54000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>43900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>28700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>33900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>37000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-32400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>24200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>29900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>14300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-12100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>27800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>29900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>17200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>7900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>28800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>43700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>38800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>51100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E27" s="3">
         <v>69800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>68400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>62600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>23400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>83700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>60200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>51500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>24800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>54000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>43900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>28700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>33900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>37000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-32400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>24200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>29900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>14300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-12100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>27800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>29900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>17200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>7900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>28800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>43700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>38800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>51100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2848,8 +2906,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2880,8 +2941,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
@@ -2898,35 +2959,35 @@
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3">
         <v>2600</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>-1100</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2934,12 +2995,12 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>32200</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2955,8 +3016,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3062,8 +3126,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3169,222 +3236,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AJ32" s="3">
         <v>-1000</v>
       </c>
       <c r="AK32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E33" s="3">
         <v>69800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>68400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>62600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>23400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>83700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>60200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>51500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>24800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>54000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>43900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>28700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>33900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>37000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-32400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-11200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>24200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>29900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>14300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-12100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>27800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>29900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>17200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>40100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>28800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>43700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>38800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>51100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3490,227 +3566,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E35" s="3">
         <v>69800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>68400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>62600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>23400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>83700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>60200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>51500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>24800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>54000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>43900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>28700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>33900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>37000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-32400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-11200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>24200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>29900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>14300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-12100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>27800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>29900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>17200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>40100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>28800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>43700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>38800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>51100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45682</v>
+      </c>
+      <c r="E38" s="2">
         <v>45591</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45500</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45409</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45318</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45227</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45136</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45045</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44954</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44863</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44772</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44590</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44499</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44317</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44226</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44128</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44037</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43946</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43855</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43764</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43673</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43582</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43491</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43400</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43309</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43218</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43127</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43036</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42945</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42854</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42672</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3748,8 +3833,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3787,142 +3873,146 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>92700</v>
+      </c>
+      <c r="E41" s="3">
         <v>15300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>26100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>101100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>83400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>71400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>224200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>65300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>120300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>185600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>310800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>263700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>261900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>330600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>22500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>643900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>54600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>11800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>33600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>128300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>21500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>23900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>57900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>84000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>24500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>38600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>19400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>29500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>21700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E42" s="3">
         <v>15200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>22300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>21000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>20200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>20000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>22300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>20400</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -4001,222 +4091,231 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1441300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1723700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1588000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1442300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1298700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1535000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1303400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1243600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1114900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1297800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1170700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1043300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>933200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1077900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1102800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1048500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1057000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1144300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1156600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1145800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1073600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1262900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1156800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1001900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>844600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1003300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>863500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>763100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>332600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>349600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>377300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>355100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>335500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>329800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>127300</v>
+      </c>
+      <c r="E44" s="3">
         <v>116000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>101200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>104000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>108600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>114000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>117200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>115700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>115000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>107100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>98900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>94100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>81300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>69900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>69700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>71100</v>
-      </c>
-      <c r="S44" s="3">
-        <v>70800</v>
       </c>
       <c r="T44" s="3">
         <v>70800</v>
       </c>
       <c r="U44" s="3">
+        <v>70800</v>
+      </c>
+      <c r="V44" s="3">
         <v>77800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>92600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>98300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>104900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>107400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>105200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>94400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>90800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>87800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>84300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>448500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>490400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>472500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>529100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>481600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>570000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>450600</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4241,196 +4340,202 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>38600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>42800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>43900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>47000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>30900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>37500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>43300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>47900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>38400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>49700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>48600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>31800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>32300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>31100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>37800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>29100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>33300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>30100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>30800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>39700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>28800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>50100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>46700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>41700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>45400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1694600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1896800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1760700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1626800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1550000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1708700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1555200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1483800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1492700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1513000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1433800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1370000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1356100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1449000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1477700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1498100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1168600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1265500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1306600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1930900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1258300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1411900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1307800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1178500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1096400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1148900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1005300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>936100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>904800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>893400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>938500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>950200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>888300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>966900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>851200</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4455,63 +4560,63 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>8300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>12500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>14100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>15300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>16700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>16200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>17600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>18600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>19900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>21300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>22700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>24200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>26200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>28400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>55200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>32000</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4536,222 +4641,231 @@
       <c r="AK47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>654100</v>
+      </c>
+      <c r="E48" s="3">
         <v>622800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>563000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>538700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>521300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>505100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>466000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>447100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>435100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>403300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>377600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>361100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>355900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>346200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>343600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>340500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>337100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>354200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>385500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>422100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>446200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>463000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>491700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>498400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>424800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>428300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>423700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>416300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>414800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>423300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>422100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>378400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>344100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>337700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>550100</v>
+      </c>
+      <c r="E49" s="3">
         <v>560000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>429500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>423800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>420900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>425700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>352100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>355600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>359100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>362600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>366500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>370400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>374300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>378300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>382500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>387100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>391800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>397000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>402000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>407200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>465700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>470900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>476200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>481500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>486900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>492300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>498100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>503900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>493200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>499100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>505300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>513100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>498200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>500300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>508000</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4857,8 +4971,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4964,115 +5081,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E52" s="3">
         <v>29800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>20700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>17900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>18100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>21400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>21100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>29000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>29700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>30600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>31400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>24800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>25500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>26400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>24400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>34200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>31700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>25400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>26800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>28200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>36800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>33400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>34300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>35800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>33500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5178,115 +5301,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2945400</v>
+      </c>
+      <c r="E54" s="3">
         <v>3114700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2779400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2611600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2516900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2664200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2395600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2311700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2313300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2305300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2206400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2132100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2118200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2204700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2241900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2263000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1944200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2065100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2144700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2812900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2217600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2395600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2328400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2211200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2097500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2133200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1952400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1883000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1841000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1852500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1899300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1876000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1766400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1838400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1719700</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5324,8 +5453,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5363,141 +5493,145 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>223500</v>
+      </c>
+      <c r="E57" s="3">
         <v>241000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>233500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>212900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>222100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>215300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>204800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>196200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>207700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>201000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>187600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>176400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>155900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>173600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>173200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>171000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>159000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>183700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>177300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>194400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>119600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>129500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>140300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>138700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>119500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>134700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>125700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>112200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>92400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>109900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>133000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>119300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>99300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>114700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>115500</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E58" s="3">
         <v>39800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>33300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>50400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>49500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>47600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>46800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>46100</v>
-      </c>
-      <c r="K58" s="3">
-        <v>17500</v>
       </c>
       <c r="L58" s="3">
         <v>17500</v>
@@ -5512,22 +5646,22 @@
         <v>17500</v>
       </c>
       <c r="P58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="Q58" s="3">
         <v>13100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>66600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>61500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>81700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>78100</v>
-      </c>
-      <c r="U58" s="3">
-        <v>22500</v>
       </c>
       <c r="V58" s="3">
         <v>22500</v>
@@ -5539,474 +5673,489 @@
         <v>22500</v>
       </c>
       <c r="Y58" s="3">
+        <v>22500</v>
+      </c>
+      <c r="Z58" s="3">
         <v>16900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>11300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5600</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
       <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
         <v>31300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>28900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>26500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>24100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>21700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>14400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>18800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>17500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>140300</v>
+      </c>
+      <c r="E59" s="3">
         <v>136900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>67600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>103600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>73700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>61700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>57400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>68100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>244300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>252600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>227100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>201700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>208400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>206400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>207600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>203500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>207800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>201900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>211500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>211400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>180900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>212800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>199800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>191700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>159900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>169300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>153300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>134800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>140800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>149200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>163900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>155100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>145000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>179700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>587200</v>
+      </c>
+      <c r="E60" s="3">
         <v>608500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>511100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>513600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>506300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>488800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>459400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>433100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>469600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>471100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>432100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>395700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>381800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>393200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>447500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>436100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>448500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>463700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>411300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>428300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>323000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>364800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>357000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>341700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>285000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>304000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>310300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>275900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>259600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>283100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>318500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>288900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>263200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>312000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>322600</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1010100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1165700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>988600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>889500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>835500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>993300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>842600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>846900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>807400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>811400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>815300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>819300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>823300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>827200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>831200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>835200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>501600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>490000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>665500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1363900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>844400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>970200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>932300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>867400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>867600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>867800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>727300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>731700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>733800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>736000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>738300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>811600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>740600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>774500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>706200</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>76800</v>
+      </c>
+      <c r="E62" s="3">
         <v>75100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>77300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>76200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>70800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>70200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>68300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>72100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>167600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>164200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>161900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>158800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>154600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>173500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>182700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>181800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>182800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>198200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>194100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>186800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>181600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>180400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>185700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>181000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>140800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>144500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>131500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>128400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>122500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>143800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>170900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>152800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>147600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>138200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6112,8 +6261,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6219,8 +6371,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6326,115 +6481,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1706300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1881000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1620900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1531000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1462200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1610200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1431600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1414300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1444500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1446700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1409400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1373800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1359700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1393900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1461400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1453100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1132900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1151900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1270900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1979000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1349000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1515400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1474900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1390000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1293300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1316400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1169200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1136000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1116000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1162900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1227700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1253300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1151400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1224700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1162400</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6472,8 +6633,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6579,8 +6741,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6686,8 +6851,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6793,8 +6961,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6900,115 +7071,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1220400</v>
+      </c>
+      <c r="E72" s="3">
         <v>1201300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1131500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1063100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1040300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1026600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>942800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>882600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>855100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>838300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>784300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>747100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>748400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>798500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>769800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>797700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>800600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>867800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>833800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>796800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>829700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>840900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>816700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>786800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>772500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>784500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>756700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>726800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>709600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>674200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>652300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>608600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>600500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>588900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>537900</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7114,8 +7291,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7221,8 +7401,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7328,115 +7511,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1239100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1233700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1158400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1080600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1054700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1053900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>964000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>897400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>868800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>858600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>797000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>758300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>758500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>810800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>780400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>810000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>811300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>913100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>873700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>833900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>868600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>880200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>853400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>821200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>804200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>816900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>783200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>747000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>725000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>689600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>671600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>622700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>615100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>613700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>557300</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7542,227 +7731,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45682</v>
+      </c>
+      <c r="E80" s="2">
         <v>45591</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45500</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45409</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45318</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45227</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45136</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45045</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44954</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44863</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44772</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44590</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44499</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44317</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44226</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44128</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44037</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43946</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43855</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43764</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43673</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43582</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43491</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43400</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43309</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43218</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43127</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43036</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42945</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42854</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42763</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42672</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E81" s="3">
         <v>69800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>68400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>62600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>23400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>83700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>60200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>51500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>24800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>54000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>43900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>28700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>33900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>37000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-32400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-11200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>24200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>29900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>14300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-12100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>27800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>29900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>17200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>40100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>28800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>43700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>38800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>51100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7800,115 +7998,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E83" s="3">
         <v>36500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>34500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>33800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>33100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>31600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>31400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>32700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>36700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>35500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>35300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>36600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>37300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>37800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>38500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>39100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>43600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>42300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>44100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>45900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>46600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>47400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>47200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>46300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>45900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>45500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>44800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>43400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>42400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>42700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>40200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>37400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>35700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>34500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8014,8 +8216,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8121,8 +8326,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8228,8 +8436,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8335,8 +8546,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8442,115 +8656,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>328200</v>
+      </c>
+      <c r="E89" s="3">
         <v>65800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-37400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>325100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-37300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>56300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-85100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>246200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-64900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>145500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>104300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>17300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>41500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>102400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>111900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>82300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>85200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>191800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-53600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-56100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>142800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-55500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>12600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>24600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>103700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>56800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>149900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>42300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>105800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-41600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>182500</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8588,115 +8808,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-68500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-74600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-65400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-42000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-57400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-67200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-51000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-42900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-65200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-54800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-42500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-38400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-43600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-45100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-36700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-31600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-21900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-20700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-18700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-17900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-38200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-45800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-47300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-31800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-58300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-40100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-47300</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8802,8 +9026,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8909,115 +9136,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-59800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-216500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-76700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-42200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-52700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-179900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-40000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-33600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-62600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-49200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-39100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-33000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-43400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-44100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-35500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-28600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-20400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-18300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-15800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-14500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-32500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-42600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-39100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-45800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-78400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-32900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-38200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-151600</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9055,8 +9288,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9081,8 +9315,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -9162,8 +9396,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9269,8 +9506,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9376,8 +9616,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9483,115 +9726,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-191000</v>
+      </c>
+      <c r="E100" s="3">
         <v>146400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>77700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-187000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>149500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-34100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-24700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-27200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-55100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-58400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-50400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>305900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-85500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-119000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-701200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>522300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-133200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>37800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>65100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>95700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-22800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>25900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-65100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>67700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-16500</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9616,8 +9865,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9697,111 +9946,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-74900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>85400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-67700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-152800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>158900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-55000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-65300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-125200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>47100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-68700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>318800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-10500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-621300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>589100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>42700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-95300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>105800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-33400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-26100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>59500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>19300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>7800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-12100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>14500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="92">
   <si>
     <t>DY</t>
   </si>
@@ -656,494 +656,519 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45864</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45773</v>
+      </c>
+      <c r="F7" s="2">
         <v>45682</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45591</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45500</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45409</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45318</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45227</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45136</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45045</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44954</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44863</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44772</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44590</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44499</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44317</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44226</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44128</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44037</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43946</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43855</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43764</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43673</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43582</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43491</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43400</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43309</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43218</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43127</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43036</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42945</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42763</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42672</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1258600</v>
+      </c>
+      <c r="F8" s="3">
         <v>1084500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1272000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1203100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1142400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>952500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1136100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1041500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1045500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>917500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1042400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>972300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>876300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>761500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>854000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>787600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>727500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>750700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>810300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>823900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>814300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>737600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>884100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>884200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>833700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>748600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>848200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>799500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>731400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>655100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>756200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>780200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>786300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>701100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>799200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>789200</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1011100</v>
+      </c>
+      <c r="F9" s="3">
         <v>887900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1007400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>952900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>921600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>791400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>886700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>830400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>853400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>765700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>850900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>798000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>745700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>656600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>705900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>651400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>620000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>645500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>658400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>658000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>680200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>633200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>724400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>720400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>701800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>633300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>687200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>642400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>599600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>540600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>600800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>606900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>621500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>561400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>615000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>605900</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>247500</v>
+      </c>
+      <c r="F10" s="3">
         <v>196600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>264600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>250200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>220800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>161100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>249400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>211100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>192100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>151800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>191500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>174300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>130600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>104900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>148100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>136200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>107500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>105200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>151900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>165900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>134100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>104400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>159700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>163800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>131900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>115300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>161000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>157100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>131800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>114500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>155400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>173300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>164800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>139700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>184200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>183300</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1182,8 +1207,10 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1292,8 +1319,14 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1402,80 +1435,86 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F14" s="3">
         <v>-7700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-4000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-7200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-12400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-4600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-8400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-7600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-7800</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3">
         <v>500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>40800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>100</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1485,11 +1524,11 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1500,130 +1539,142 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="3">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>58400</v>
+      </c>
+      <c r="F15" s="3">
         <v>54800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>52000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>46600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>45200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>45300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>42500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>38000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>37300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>36700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>35500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>35300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>36600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>37300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>37800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>38500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>39100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>43600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>42300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>44100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>45900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>46600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>47400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>47200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>46300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>45900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>45500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>44800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>43400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>42400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>42700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>40200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>37400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AL15" s="3">
         <v>35700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AM15" s="3">
         <v>34500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AN15" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1659,228 +1710,242 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1173200</v>
+      </c>
+      <c r="F17" s="3">
         <v>1030900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1166000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1099000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1061400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>909700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1016700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>953200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>973000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>874400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>965100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>906700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>851700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>757800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>810500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>754600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>726200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>753000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>763300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>769900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>832700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>740900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>841600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>832700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>806700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>752700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>801500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>751700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>705200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>643400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>708100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>706700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>720200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>655300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>709700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>704100</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
+        <v>85400</v>
+      </c>
+      <c r="F18" s="3">
         <v>53700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>106000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>104000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>81000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>42800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>119400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>88300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>72500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>43100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>77300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>65600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>24600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>3700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>43500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>33000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>47000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>54000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-18400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>42500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>51500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>27000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>46700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>47800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>26200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>11700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>48100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>73500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>66100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>45800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>89500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1919,558 +1984,590 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>3200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>1500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>2500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>2600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>4800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>2700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>3700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>3100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>4000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>5700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>1200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>2900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>4100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>7700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>5900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>6000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>1000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>1000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>141300</v>
+      </c>
+      <c r="F21" s="3">
         <v>107400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>156700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>148900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>123100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>87500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>160500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>124500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>106900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>80200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>115200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>103500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>66000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>41200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>81800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>72500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>43100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>42000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>93000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>101300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>28600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>43900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>91300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>102700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>79100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>43000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>95100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>96700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>77200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>54400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>96700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>119800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>108300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>82600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>125000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>124700</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F22" s="3">
         <v>16100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>17500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>14700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>12800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>15000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>14000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>12300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>11400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>11600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>10600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>9300</v>
-      </c>
-      <c r="O22" s="3">
-        <v>9100</v>
-      </c>
-      <c r="P22" s="3">
-        <v>8800</v>
       </c>
       <c r="Q22" s="3">
         <v>9100</v>
       </c>
       <c r="R22" s="3">
+        <v>8800</v>
+      </c>
+      <c r="S22" s="3">
+        <v>9100</v>
+      </c>
+      <c r="T22" s="3">
         <v>9300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>5900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>4700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>4700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>7900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>12500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>12600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>13100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>12900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>12200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>12400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>11300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>10400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>10200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>9900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>9700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>9700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>9400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>9200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>9100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AN22" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3">
+        <v>78600</v>
+      </c>
+      <c r="F23" s="3">
         <v>44200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>91300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>94800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>77400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>31800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>112400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>81800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>66100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>31900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>69200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>58900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>20200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>34900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>24700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-6300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>46000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>49300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-29700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-15300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>30800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>42600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>20500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>38300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>41400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>23700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>2200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>44400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>69800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>61500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>37700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>81400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3">
+        <v>17600</v>
+      </c>
+      <c r="F24" s="3">
         <v>11600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>21500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>26400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>14900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>8400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>28600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>21500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>14600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>7100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>15100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>15000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>6200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>6500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-2700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>12000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>12200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>2700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>6600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>12700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>6200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>10500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>11500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>6500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>15600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>26100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>22800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>14000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>30300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>29600</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2579,228 +2676,246 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
+        <v>61000</v>
+      </c>
+      <c r="F26" s="3">
         <v>32700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>69800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>68400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>62600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>23400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>83700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>60200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>51500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>24800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>54000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>43900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>19500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>28700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>18200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-6800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>33900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>37000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-32400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>24200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>29900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>14300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-12100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>27800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>29900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>17200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>7900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>28800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>43700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>38800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>23700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>51100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
+        <v>61000</v>
+      </c>
+      <c r="F27" s="3">
         <v>32700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>69800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>68400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>62600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>23400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>83700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>60200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>51500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>24800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>54000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>43900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>19500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>28700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>18200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-6800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>33900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>37000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-32400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-10100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>24200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>29900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>14300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-12100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>27800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>29900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>17200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>7900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>28800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>43700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>38800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>23700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>51100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2909,8 +3024,14 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2944,11 +3065,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
@@ -2962,51 +3083,51 @@
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3">
         <v>2600</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>32200</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3019,8 +3140,14 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3129,8 +3256,14 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3239,228 +3372,246 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-3200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-1500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-2500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-2600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-4800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-2700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-3700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-3100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>-4800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
+        <v>61000</v>
+      </c>
+      <c r="F33" s="3">
         <v>32700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>69800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>68400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>62600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>23400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>83700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>60200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>51500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>24800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>54000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>43900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>19500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>28700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>18200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-4200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>33900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>37000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-32400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>24200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>29900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>14300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-12100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>27800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>29900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>17200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>40100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>28800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>43700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>38800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>23700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>51100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3569,233 +3720,251 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
+        <v>61000</v>
+      </c>
+      <c r="F35" s="3">
         <v>32700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>69800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>68400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>62600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>23400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>83700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>60200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>51500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>24800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>54000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>43900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>19500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>28700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>18200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-4200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>33900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>37000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-32400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>24200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>29900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>14300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-12100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>27800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>29900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>17200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>40100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>28800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>43700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>38800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>23700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>51100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45864</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45773</v>
+      </c>
+      <c r="F38" s="2">
         <v>45682</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45591</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45500</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45409</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45318</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45227</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45136</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45045</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44954</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44863</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44772</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44590</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44499</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44317</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44226</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44128</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44037</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43946</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43855</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43764</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43673</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43582</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43491</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43400</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43309</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43218</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43127</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43036</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42945</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42763</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42672</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3834,8 +4003,10 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3874,151 +4045,159 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
+        <v>16100</v>
+      </c>
+      <c r="F41" s="3">
         <v>92700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>15300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>19600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>26100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>101100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>15700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>83400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>71400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>224200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>65300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>120300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>185600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>310800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>263700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>261900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>330600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>11800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>12000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>22500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>643900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>54600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>11800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>12600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>33600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>128300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>21500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>23900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>57900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>84000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>24500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>38600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>19400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>29500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>21700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F42" s="3">
         <v>11300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>15200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>22300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>21000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>20200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>20000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>22300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>20400</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4094,228 +4273,246 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1631500</v>
+      </c>
+      <c r="F43" s="3">
         <v>1441300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1723700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1588000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1442300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1298700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1535000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1303400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1243600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1114900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1297800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1170700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1043300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>933200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1077900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1102800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1048500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1057000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1144300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1156600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1145800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1073600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1262900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1156800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1001900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>844600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1003300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>863500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>763100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>332600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>349600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>377300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>355100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>335500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>329800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
+        <v>133000</v>
+      </c>
+      <c r="F44" s="3">
         <v>127300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>116000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>101200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>104000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>108600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>114000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>117200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>115700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>115000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>107100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>98900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>94100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>81300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>69900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>69700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>71100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>70800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>70800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>77800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>92600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>98300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>104900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>107400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>105200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>94400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>90800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>87800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>84300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>448500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>490400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>472500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>529100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>481600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>570000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>450600</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4343,199 +4540,211 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>38600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>42800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>43900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>47000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>30900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>37500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>43300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>47900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>29000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>38400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>49700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>48600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>31800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>32300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>31100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>37800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>29100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>33300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>30100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>30800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>39700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>28800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>50100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>46700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>41700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>45400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1824700</v>
+      </c>
+      <c r="F46" s="3">
         <v>1694600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1896800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1760700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1626800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1550000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1708700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1555200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1483800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1492700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1513000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1433800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1370000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1356100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1449000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1477700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1498100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1168600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1265500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1306600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1930900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1258300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1411900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1307800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1178500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1096400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1148900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1005300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>936100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>904800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>893400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>938500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>950200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>888300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>966900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>851200</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4563,66 +4772,66 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>8300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>9600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>11000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>12500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>14100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>15300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>16700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>16200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>17600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>18600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>19900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>21300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>22700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>24200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>26200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>28400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>55200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>32000</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4644,228 +4853,246 @@
       <c r="AL47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
+        <v>679400</v>
+      </c>
+      <c r="F48" s="3">
         <v>654100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>622800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>563000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>538700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>521300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>505100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>466000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>447100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>435100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>403300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>377600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>361100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>355900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>346200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>343600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>340500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>337100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>354200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>385500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>422100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>446200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>463000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>491700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>498400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>424800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>428300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>423700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>416300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>414800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>423300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>422100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>378400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>344100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>337700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3">
+        <v>538300</v>
+      </c>
+      <c r="F49" s="3">
         <v>550100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>560000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>429500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>423800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>420900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>425700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>352100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>355600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>359100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>362600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>366500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>370400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>374300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>378300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>382500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>387100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>391800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>397000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>402000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>407200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>465700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>470900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>476200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>481500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>486900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>492300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>498100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>503900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>493200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>499100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>505300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>513100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>498200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>500300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>508000</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4974,8 +5201,14 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5084,118 +5317,130 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3">
+        <v>58000</v>
+      </c>
+      <c r="F52" s="3">
         <v>41600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>29800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>20700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>19000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>19500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>17900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>13900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>15000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>18000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>16800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>17500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>18100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>17900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>15800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>21400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>21100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>29000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>29700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>30600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>31400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>24800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>25500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>26400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>24400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>34200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>31700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>25400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>26800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>28200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>36800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>33400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>34300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>35800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>33500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5304,118 +5549,130 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3105000</v>
+      </c>
+      <c r="F54" s="3">
         <v>2945400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>3114700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2779400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2611600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2516900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2664200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2395600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2311700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2313300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2305300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2206400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2132100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2118200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2204700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2241900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2263000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1944200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2065100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2144700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2812900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2217600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2395600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2328400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2211200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2097500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>2133200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1952400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1883000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1841000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1852500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>1899300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>1876000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>1766400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>1838400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>1719700</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5454,8 +5711,10 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5494,150 +5753,158 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
+        <v>259200</v>
+      </c>
+      <c r="F57" s="3">
         <v>223500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>241000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>233500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>212900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>222100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>215300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>204800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>196200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>207700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>201000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>187600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>176400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>155900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>173600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>173200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>171000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>159000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>183700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>177300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>194400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>119600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>129500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>140300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>138700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>119500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>134700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>125700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>112200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>92400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>109900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>133000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>119300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>99300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>114700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>115500</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3">
+        <v>53200</v>
+      </c>
+      <c r="F58" s="3">
         <v>45800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>39800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>33300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>50400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>49500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>47600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>46800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>46100</v>
-      </c>
-      <c r="L58" s="3">
-        <v>17500</v>
-      </c>
-      <c r="M58" s="3">
-        <v>17500</v>
       </c>
       <c r="N58" s="3">
         <v>17500</v>
@@ -5649,25 +5916,25 @@
         <v>17500</v>
       </c>
       <c r="Q58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="R58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="S58" s="3">
         <v>13100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>66600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>61500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>81700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>78100</v>
-      </c>
-      <c r="V58" s="3">
-        <v>22500</v>
-      </c>
-      <c r="W58" s="3">
-        <v>22500</v>
       </c>
       <c r="X58" s="3">
         <v>22500</v>
@@ -5676,486 +5943,516 @@
         <v>22500</v>
       </c>
       <c r="Z58" s="3">
+        <v>22500</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>22500</v>
+      </c>
+      <c r="AB58" s="3">
         <v>16900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>11300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>5600</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3">
         <v>31300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>28900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>26500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>24100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>21700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>14400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>18800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>17500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
+        <v>173600</v>
+      </c>
+      <c r="F59" s="3">
         <v>140300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>136900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>67600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>103600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>73700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>61700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>57400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>68100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>244300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>252600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>227100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>201700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>208400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>206400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>207600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>203500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>207800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>201900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>211500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>211400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>180900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>212800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>199800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>191700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>159900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>169300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>153300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>134800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>140800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>149200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>163900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>155100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>145000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>179700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3">
+        <v>631800</v>
+      </c>
+      <c r="F60" s="3">
         <v>587200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>608500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>511100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>513600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>506300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>488800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>459400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>433100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>469600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>471100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>432100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>395700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>381800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>393200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>447500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>436100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>448500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>463700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>411300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>428300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>323000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>364800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>357000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>341700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>285000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>304000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>310300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>275900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>259600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>283100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>318500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>288900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>263200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>312000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>322600</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1092500</v>
+      </c>
+      <c r="F61" s="3">
         <v>1010100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1165700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>988600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>889500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>835500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>993300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>842600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>846900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>807400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>811400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>815300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>819300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>823300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>827200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>831200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>835200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>501600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>490000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>665500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1363900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>844400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>970200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>932300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>867400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>867600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>867800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>727300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>731700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>733800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>736000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>738300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>811600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>740600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>774500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>706200</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3">
+        <v>82400</v>
+      </c>
+      <c r="F62" s="3">
         <v>76800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>75100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>77300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>76200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>70800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>70200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>68300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>72100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>167600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>164200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>161900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>158800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>154600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>173500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>182700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>181800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>182800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>198200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>194100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>186800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>181600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>180400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>185700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>181000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>140800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>144500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>131500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>128400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>122500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>143800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>170900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>152800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>147600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>138200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6264,8 +6561,14 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6374,8 +6677,14 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6484,118 +6793,130 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1838800</v>
+      </c>
+      <c r="F66" s="3">
         <v>1706300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1881000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1620900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1531000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1462200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1610200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1431600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1414300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1444500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1446700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1409400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1373800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1359700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1393900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1461400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1453100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1132900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1151900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1270900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1979000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1349000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1515400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1474900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1390000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1293300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1316400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1169200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1136000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1116000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>1162900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>1227700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>1253300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>1151400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>1224700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>1162400</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6634,8 +6955,10 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6744,8 +7067,14 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6854,8 +7183,14 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6964,8 +7299,14 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7074,118 +7415,130 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1247400</v>
+      </c>
+      <c r="F72" s="3">
         <v>1220400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1201300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1131500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1063100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1040300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1026600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>942800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>882600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>855100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>838300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>784300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>747100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>748400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>798500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>769800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>797700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>800600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>867800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>833800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>796800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>829700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>840900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>816700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>786800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>772500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>784500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>756700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>726800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>709600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>674200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>652300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>608600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>600500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>588900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>537900</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7294,8 +7647,14 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7404,8 +7763,14 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7514,118 +7879,130 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1266200</v>
+      </c>
+      <c r="F76" s="3">
         <v>1239100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1233700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1158400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1080600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1054700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1053900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>964000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>897400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>868800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>858600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>797000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>758300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>758500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>810800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>780400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>810000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>811300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>913100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>873700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>833900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>868600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>880200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>853400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>821200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>804200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>816900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>783200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>747000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>725000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>689600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>671600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>622700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>615100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>613700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>557300</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7734,233 +8111,251 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45864</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45773</v>
+      </c>
+      <c r="F80" s="2">
         <v>45682</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45591</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45500</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45409</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45318</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45227</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45136</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45045</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44954</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44863</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44772</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44590</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44499</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44317</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44226</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44128</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44037</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43946</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43855</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43764</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43673</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43582</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43491</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43400</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43309</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43218</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43127</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43036</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42945</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42763</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42672</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
+        <v>61000</v>
+      </c>
+      <c r="F81" s="3">
         <v>32700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>69800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>68400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>62600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>23400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>83700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>60200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>51500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>24800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>54000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>43900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>19500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>28700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>18200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-4200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>33900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>37000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-32400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-11200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>24200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>29900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>14300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-12100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>27800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>29900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>17200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>40100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>28800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>43700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>38800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>23700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>51100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7999,118 +8394,126 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>39400</v>
+      </c>
+      <c r="F83" s="3">
         <v>38500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>36500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>34500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>33800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>33100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>31600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>31400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>32700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>36700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>35500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>35300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>36600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>37300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>37800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>38500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>39100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>43600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>42300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>44100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>45900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>46600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>47400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>47200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>46300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>45900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>45500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>44800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>43400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>42400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>42700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>40200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>37400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>35700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>34500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8219,8 +8622,14 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8329,8 +8738,14 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8439,8 +8854,14 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8549,8 +8970,14 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8659,118 +9086,130 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="F89" s="3">
         <v>328200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>65800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-7500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-37400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>325100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-37300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>56300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-85100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>246200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-4500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-12000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-64900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>145500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>104300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>17300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>41500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>102400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>111900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>82300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>85200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>191800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-24000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-53600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-56100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>142800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-55500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>12600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>24600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>103700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>56800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>149900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>42300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>105800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>-41600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>182500</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8809,118 +9248,126 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-79500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-68500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-74600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-65400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-42000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-57400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-67200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-51000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-42900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-65200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-54800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-42500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-38400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-43600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-45100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-36700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-31600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-21900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-9400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-6000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-20700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-18700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-17900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-45800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-47300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-31800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-58300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-40100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-47300</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9029,8 +9476,14 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9139,118 +9592,130 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-68600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-59800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-216500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-76700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-42200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-52700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-179900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-40000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-33600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-62600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-49200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-39100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-33000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-43400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-44100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-35500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-28600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-20400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-3500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-2500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-18300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-15800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-14500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-32500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-42600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-39100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-45800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-78400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-32900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-38200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-151600</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9289,8 +9754,10 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9318,11 +9785,11 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9399,8 +9866,14 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9509,8 +9982,14 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9619,8 +10098,14 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9729,118 +10214,130 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
+        <v>45900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-191000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>146400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>77700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>4700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-187000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>149500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-4300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-34100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-24700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-14200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-27200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-55100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-58400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-50400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>305900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-85500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-119000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-701200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>522300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-133200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>37800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>65100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>95700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-22800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>25900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-65100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>67700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-16500</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9868,11 +10365,11 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9949,114 +10446,126 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-76700</v>
+      </c>
+      <c r="F102" s="3">
         <v>77400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-4300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-6600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-74900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>85400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-67700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>12000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-152800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>158900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-55000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-65300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-125200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>47100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>1800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-68700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>318800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-3600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-10500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-621300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>589100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>42700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-95300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>105800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-33400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-26100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>59500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>19300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>7800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-12100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>14500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>DY</t>
   </si>
@@ -656,532 +656,545 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
         <v>45955</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45864</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45773</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45682</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45591</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45500</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45409</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45318</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45227</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45136</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45045</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44954</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44863</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44772</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44590</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44499</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44317</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44226</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44128</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44037</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43946</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43855</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43764</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43673</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43582</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43491</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43400</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43309</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43218</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43127</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43036</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42945</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42854</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42763</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42672</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1457600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1451800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1377900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1258600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1084500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1272000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1203100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1142400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>952500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1136100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1041500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1045500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>917500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1042400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>972300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>876300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>761500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>854000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>787600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>727500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>750700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>810300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>823900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>814300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>737600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>884100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>884200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>833700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>748600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>848200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>799500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>731400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>655100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>756200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>780200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>786300</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>701100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>799200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>789200</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1192600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1131600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1070500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1011100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>887900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1007400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>952900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>921600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>791400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>886700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>830400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>853400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>765700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>850900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>798000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>745700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>656600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>705900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>651400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>620000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>645500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>658400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>658000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>680200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>633200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>724400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>720400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>701800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>633300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>687200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>642400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>599600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>540600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>600800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>606900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>621500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>561400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>615000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>605900</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>264900</v>
+      </c>
+      <c r="E10" s="3">
         <v>320200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>307500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>247500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>196600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>264600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>250200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>220800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>161100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>249400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>211100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>192100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>151800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>191500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>174300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>130600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>104900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>148100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>136200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>107500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>105200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>151900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>165900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>134100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>104400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>159700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>163800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>131900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>115300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>161000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>157100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>131800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>114500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>155400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>173300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>164800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>139700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>184200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>183300</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1223,8 +1236,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1342,8 +1356,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1461,52 +1478,55 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-10100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-9800</v>
       </c>
-      <c r="G14" s="3">
-        <v>-7700</v>
-      </c>
       <c r="H14" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I14" s="3">
         <v>-4000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-7200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-12400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-8400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-7600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-7800</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1514,33 +1534,33 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>40800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>100</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1553,8 +1573,8 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1568,139 +1588,145 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
-      <c r="AL14" s="3" t="s">
-        <v>8</v>
+      <c r="AL14" s="3">
+        <v>0</v>
       </c>
       <c r="AM14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
+      <c r="AN14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>88200</v>
+      </c>
+      <c r="E15" s="3">
         <v>62200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>60900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>58400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>54800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>52000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>46600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>45200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>45300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>42500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>38000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>37300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>36700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>35500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>35300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>36600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>37300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>37800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>38500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>39100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>43600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>42300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>44100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>45900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>46600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>47400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>47200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>46300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>45900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>45500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>44800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>43400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>42400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>42700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>40200</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>37400</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>35700</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>34500</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1739,246 +1765,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1389700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1301100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1238100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1173200</v>
       </c>
-      <c r="G17" s="3">
-        <v>1030900</v>
-      </c>
       <c r="H17" s="3">
+        <v>1019500</v>
+      </c>
+      <c r="I17" s="3">
         <v>1166000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1099000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1061400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>909700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1016700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>953200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>973000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>874400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>965100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>906700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>851700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>757800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>810500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>754600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>726200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>753000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>763300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>769900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>832700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>740900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>841600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>832700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>806700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>752700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>801500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>751700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>705200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>643400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>708100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>706700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>720200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>655300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>709700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>704100</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E18" s="3">
         <v>150700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>139800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>85400</v>
       </c>
-      <c r="G18" s="3">
-        <v>53700</v>
-      </c>
       <c r="H18" s="3">
+        <v>65100</v>
+      </c>
+      <c r="I18" s="3">
         <v>106000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>104000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>81000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>42800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>119400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>88300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>72500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>43100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>77300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>65600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>24600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>43500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>33000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>47000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>54000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-18400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>42500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>51500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>27000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>46700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>47800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>26200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>11700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>48100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>73500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>66100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>45800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>89500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2020,603 +2053,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E20" s="3">
         <v>1500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>4100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>7700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>5900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>6000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>4800</v>
-      </c>
-      <c r="AM20" s="3">
-        <v>1000</v>
       </c>
       <c r="AN20" s="3">
         <v>1000</v>
       </c>
       <c r="AO20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AP20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>153200</v>
+      </c>
+      <c r="E21" s="3">
         <v>211400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>197400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>141300</v>
       </c>
-      <c r="G21" s="3">
-        <v>107400</v>
-      </c>
       <c r="H21" s="3">
+        <v>118800</v>
+      </c>
+      <c r="I21" s="3">
         <v>156700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>148900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>123100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>87500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>160500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>124500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>106900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>80200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>115200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>103500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>66000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>41200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>81800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>72500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>43100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>42000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>93000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>101300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>28600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>43900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>91300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>102700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>79100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>43000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>95100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>96700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>77200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>54400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>96700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>119800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>108300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>82600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>125000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>124700</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E22" s="3">
         <v>13800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>15000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>10600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>9300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>5900</v>
-      </c>
-      <c r="W22" s="3">
-        <v>4700</v>
       </c>
       <c r="X22" s="3">
         <v>4700</v>
       </c>
       <c r="Y22" s="3">
+        <v>4700</v>
+      </c>
+      <c r="Z22" s="3">
         <v>7900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>12500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>12600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>13100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>12200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>12400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>11300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>10400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>10200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>9900</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>9700</v>
       </c>
       <c r="AK22" s="3">
         <v>9700</v>
       </c>
       <c r="AL22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AM22" s="3">
         <v>9400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>9200</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>9100</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E23" s="3">
         <v>140300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>131100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>78600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>44200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>91300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>94800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>77400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>31800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>112400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>81800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>66100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>31900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>69200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>58900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>20200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>34900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>24700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>46000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>49300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-29700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-15300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>30800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>42600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>20500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>38300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>41400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>23700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>44400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>69800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>61500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>37700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>81400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E24" s="3">
         <v>33900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>33600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>17600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>26400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>28600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>21500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-5700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-2700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>12000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>12200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>12700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>10500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>11500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>15600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>26100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>22800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>14000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>30300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>29600</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2734,246 +2783,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E26" s="3">
         <v>106400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>97500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>61000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>32700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>69800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>68400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>62600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>23400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>83700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>60200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>51500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>24800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>54000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>43900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>28700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>18200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>33900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>37000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-32400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>24200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>29900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>14300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-12100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>27800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>29900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>17200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>28800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>43700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>38800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>23700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>51100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E27" s="3">
         <v>106400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>97500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>61000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>32700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>69800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>68400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>62600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>23400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>83700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>60200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>51500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>24800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>54000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>43900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>28700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>18200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>33900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>37000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-32400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-10100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>24200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>29900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>14300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-12100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>27800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>29900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>17200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>7900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>28800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>43700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>38800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>23700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>51100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3091,8 +3149,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3135,8 +3196,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -3153,35 +3214,35 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>2600</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3189,12 +3250,12 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>32200</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3210,8 +3271,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3329,8 +3393,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3448,246 +3515,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="AM32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AN32" s="3">
         <v>-1000</v>
       </c>
       <c r="AO32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AP32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E33" s="3">
         <v>106400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>97500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>61000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>32700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>69800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>68400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>62600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>23400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>83700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>60200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>51500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>24800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>54000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>43900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>28700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>18200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>33900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>37000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-32400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>24200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>29900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>14300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-12100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>27800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>29900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>17200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>40100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>28800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>43700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>38800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>23700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>51100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3805,251 +3881,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E35" s="3">
         <v>106400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>97500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>61000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>32700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>69800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>68400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>62600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>23400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>83700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>60200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>51500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>24800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>54000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>43900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>28700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>18200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>33900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>37000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-32400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>24200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>29900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>14300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-12100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>27800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>29900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>17200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>40100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>28800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>43700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>38800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>23700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>51100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
         <v>45955</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45864</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45773</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45682</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45591</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45500</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45409</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45318</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45227</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45136</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45045</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44954</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44863</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44772</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44590</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44499</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44317</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44226</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44128</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44037</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43946</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43855</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43764</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43673</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43582</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43491</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43400</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43309</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43218</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43127</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43036</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42945</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42854</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42763</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42672</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4091,8 +4176,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4134,166 +4220,170 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>709200</v>
+      </c>
+      <c r="E41" s="3">
         <v>110100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>28500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>92700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>101100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>15700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>83400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>71400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>224200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>65300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>120300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>185600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>310800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>263700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>261900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>330600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>11800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>22500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>643900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>54600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>12600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>33600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>128300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>21500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>23900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>57900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>84000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>24500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>38600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>19400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>29500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>21700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E42" s="3">
         <v>10300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>11300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>15200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>22300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>21000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>20200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>20000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>22300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>20400</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4372,246 +4462,255 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1879200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1755800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1744900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1631500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1441300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1723700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1588000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1442300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1298700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1535000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1303400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1243600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1114900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1297800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1170700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1043300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>933200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1077900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1102800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1048500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1057000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1144300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1156600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1145800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1073600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1262900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1156800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1001900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>844600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1003300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>863500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>763100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>332600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>349600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>377300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>355100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>335500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>329800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>128300</v>
+      </c>
+      <c r="E44" s="3">
         <v>120100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>122600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>133000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>127300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>116000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>101200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>104000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>108600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>114000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>117200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>115700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>115000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>107100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>98900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>94100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>81300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>69900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>69700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>71100</v>
-      </c>
-      <c r="W44" s="3">
-        <v>70800</v>
       </c>
       <c r="X44" s="3">
         <v>70800</v>
       </c>
       <c r="Y44" s="3">
+        <v>70800</v>
+      </c>
+      <c r="Z44" s="3">
         <v>77800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>92600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>98300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>104900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>107400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>105200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>94400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>90800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>87800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>84300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>448500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>490400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>472500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>529100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>481600</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>570000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>450600</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4648,208 +4747,214 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>38600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>42800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>43900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>47000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>30900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>37500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>43300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>47900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>29000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>38400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>49700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>48600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>31800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>32300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>31100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>37800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>29100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>33300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>30100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>30800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>39700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>28800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>50100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>46700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>41700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>45400</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2756900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2026000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1938900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1824700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1694600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1896800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1760700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1626800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1550000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1708700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1555200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1483800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1492700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1513000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1433800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1370000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1356100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1449000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1477700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1498100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1168600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1265500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1306600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1930900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1258300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1411900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1307800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1178500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1096400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1148900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1005300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>936100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>904800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>893400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>938500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>950200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>888300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>966900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>851200</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4886,63 +4991,63 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
         <v>8300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>12500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>14100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>15300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>16700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>16200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>17600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>18600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>19900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>21300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>22700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>24200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>26200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>28400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>55200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>32000</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
@@ -4967,246 +5072,255 @@
       <c r="AO47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>745000</v>
+      </c>
+      <c r="E48" s="3">
         <v>686700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>676800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>679400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>654100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>622800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>563000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>538700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>521300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>505100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>466000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>447100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>435100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>403300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>377600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>361100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>355900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>346200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>343600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>340500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>337100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>354200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>385500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>422100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>446200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>463000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>491700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>498400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>424800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>428300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>423700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>416300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>414800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>423300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>422100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>378400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>344100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>337700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2369400</v>
+      </c>
+      <c r="E49" s="3">
         <v>572200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>582000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>538300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>550100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>560000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>429500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>423800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>420900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>425700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>352100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>355600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>359100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>362600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>366500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>370400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>374300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>378300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>382500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>387100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>391800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>397000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>402000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>407200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>465700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>470900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>476200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>481500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>486900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>492300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>498100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>503900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>493200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>499100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>505300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>513100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>498200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>500300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>508000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5324,8 +5438,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5443,127 +5560,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>97300</v>
+      </c>
+      <c r="E52" s="3">
         <v>35900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>17900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>58000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>41600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>29800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>19000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>17900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>18000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>16800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>17500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>18100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>15800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>21400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>21100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>29000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>29700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>30600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>31400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>24800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>25500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>26400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>24400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>34200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>31700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>25400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>26800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>28200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>36800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>33400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>34300</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>35800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>33500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5681,127 +5804,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5979200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3324800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3219900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3105000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2945400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3114700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2779400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2611600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2516900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2664200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2395600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2311700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2313300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2305300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2206400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2132100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2118200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2204700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2241900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2263000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1944200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2065100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2144700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2812900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2217600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2395600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2328400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2211200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2097500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2133200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1952400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1883000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1841000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1852500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1899300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1876000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1766400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1838400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1719700</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5843,8 +5972,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5886,165 +6016,169 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>497300</v>
+      </c>
+      <c r="E57" s="3">
         <v>297100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>264900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>259200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>223500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>241000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>233500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>212900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>222100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>215300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>204800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>196200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>207700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>201000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>187600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>176400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>155900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>173600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>173200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>171000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>159000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>183700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>177300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>194400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>119600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>129500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>140300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>138700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>119500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>134700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>125700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>112200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>92400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>109900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>133000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>119300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>99300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>114700</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>115500</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E58" s="3">
         <v>58100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>59200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>53200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>45800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>39800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>33300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>50400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>49500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>47600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>46800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>46100</v>
-      </c>
-      <c r="O58" s="3">
-        <v>17500</v>
       </c>
       <c r="P58" s="3">
         <v>17500</v>
@@ -6059,22 +6193,22 @@
         <v>17500</v>
       </c>
       <c r="T58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="U58" s="3">
         <v>13100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>66600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>61500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>81700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>78100</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>22500</v>
       </c>
       <c r="Z58" s="3">
         <v>22500</v>
@@ -6086,522 +6220,537 @@
         <v>22500</v>
       </c>
       <c r="AC58" s="3">
+        <v>22500</v>
+      </c>
+      <c r="AD58" s="3">
         <v>16900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>11300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>5600</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
-      </c>
       <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
         <v>31300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>28900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>26500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>24100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>21700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>14400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>18800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>17500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>207200</v>
+      </c>
+      <c r="E59" s="3">
         <v>103500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>110800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>173600</v>
       </c>
-      <c r="G59" s="3">
-        <v>140300</v>
-      </c>
       <c r="H59" s="3">
+        <v>141700</v>
+      </c>
+      <c r="I59" s="3">
         <v>136900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>67600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>103600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>73700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>61700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>57400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>68100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>244300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>252600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>227100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>201700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>208400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>206400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>207600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>203500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>207800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>201900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>211500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>211400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>180900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>212800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>199800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>191700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>159900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>169300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>153300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>134800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>140800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>149200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>163900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>155100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>145000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>179700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1006900</v>
+      </c>
+      <c r="E60" s="3">
         <v>656500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>612700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>631800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>587200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>608500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>511100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>513600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>506300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>488800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>459400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>433100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>469600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>471100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>432100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>395700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>381800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>393200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>447500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>436100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>448500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>463700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>411300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>428300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>323000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>364800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>357000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>341700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>285000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>304000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>310300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>275900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>259600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>283100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>318500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>288900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>263200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>312000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>322600</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2945700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1006500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1087600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1092500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1010100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1165700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>988600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>889500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>835500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>993300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>842600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>846900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>807400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>811400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>815300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>819300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>823300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>827200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>831200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>835200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>501600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>490000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>665500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1363900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>844400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>970200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>932300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>867400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>867600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>867800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>727300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>731700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>733800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>736000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>738300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>811600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>740600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>774500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>706200</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E62" s="3">
         <v>93500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>82200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>82400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>76800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>75100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>77300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>76200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>70800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>70200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>68300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>72100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>167600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>164200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>161900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>158800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>154600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>173500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>182700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>181800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>182800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>198200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>194100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>186800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>181600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>180400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>185700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>181000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>140800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>144500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>131500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>128400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>122500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>143800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>170900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>152800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>147600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>138200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6719,8 +6868,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6838,8 +6990,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6957,127 +7112,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4120000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1841500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1850200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1838800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1706300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1881000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1620900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1531000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1462200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1610200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1431600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1414300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1444500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1446700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1409400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1373800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1359700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1393900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1461400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1453100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1132900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1151900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1270900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1979000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1349000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1515400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1474900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1390000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1293300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1316400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1169200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1136000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1116000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1162900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1227700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1253300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1151400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1224700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1162400</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7119,8 +7280,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7238,8 +7400,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7357,8 +7522,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7476,8 +7644,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7595,127 +7766,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1467500</v>
+      </c>
+      <c r="E72" s="3">
         <v>1451300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1344900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1247400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1220400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1201300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1131500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1063100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1040300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1026600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>942800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>882600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>855100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>838300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>784300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>747100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>748400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>798500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>769800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>797700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>800600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>867800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>833800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>796800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>829700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>840900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>816700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>786800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>772500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>784500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>756700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>726800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>709600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>674200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>652300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>608600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>600500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>588900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>537900</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7833,8 +8010,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7952,8 +8132,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8071,127 +8254,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1859100</v>
+      </c>
+      <c r="E76" s="3">
         <v>1483300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1369700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1266200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1239100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1233700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1158400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1080600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1054700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1053900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>964000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>897400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>868800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>858600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>797000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>758300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>758500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>810800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>780400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>810000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>811300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>913100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>873700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>833900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>868600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>880200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>853400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>821200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>804200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>816900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>783200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>747000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>725000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>689600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>671600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>622700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>615100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>613700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>557300</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8309,251 +8498,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
         <v>45955</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45864</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45773</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45682</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45591</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45500</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45409</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45318</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45227</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45136</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45045</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44954</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44863</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44772</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44590</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44499</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44317</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44226</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44128</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44037</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43946</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43855</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43764</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43673</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43582</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43491</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43400</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43309</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43218</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43127</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43036</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42945</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42854</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42763</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42672</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E81" s="3">
         <v>106400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>97500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>61000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>32700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>69800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>68400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>62600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>23400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>83700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>60200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>51500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>24800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>54000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>43900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>28700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>18200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>33900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>37000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-32400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>24200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>29900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>14300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-12100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>27800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>29900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>17200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>40100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>28800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>43700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>38800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>23700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>51100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8595,127 +8793,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E83" s="3">
         <v>42500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>40600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>39400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>38500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>36500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>34500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>33800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>33100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>31600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>31400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>36700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>35500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>35300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>36600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>37300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>37800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>38500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>39100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>43600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>42300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>44100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>45900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>46600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>47400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>47200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>46300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>45900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>45500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>44800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>43400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>42400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>42700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>40200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>37400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>35700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>34500</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8833,8 +9035,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8952,8 +9157,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9071,8 +9279,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9190,8 +9401,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9309,127 +9523,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>419000</v>
+      </c>
+      <c r="E89" s="3">
         <v>220000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>57400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-54000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>328200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>65800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-37400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>325100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-37300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>56300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-85100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>246200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-12000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-64900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>145500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>104300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>17300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>41500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>102400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>111900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>82300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>85200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>191800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-24000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-53600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-56100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>142800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-55500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>12600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>24600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>103700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>56800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>149900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>42300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>105800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-41600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>182500</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9471,127 +9691,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-55200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-51700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-79500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-68500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-74600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-65400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-42000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-57400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-67200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-51000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-42900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-65200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-54800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-42500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-38400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-43600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-45100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-36700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-31600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-21900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-18700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-45800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-47300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-31800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-58300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-40100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-47300</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9709,8 +9933,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9828,127 +10055,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1680500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-47600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-39100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-68600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-59800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-216500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-76700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-42200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-52700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-179900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-40000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-33600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-62600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-49200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-39100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-33000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-43400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-44100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-35500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-28600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-20400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-18300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-15800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-14500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-32500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-42600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-39100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-45800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-78400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-32900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-38200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-151600</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9990,8 +10223,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10028,8 +10262,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -10109,8 +10343,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10228,8 +10465,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10347,8 +10587,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10466,127 +10709,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1860500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-90800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>45900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-191000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>146400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>77700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-187000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>149500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-34100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-24700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-14200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-27200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-55100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-58400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-50400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>305900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-85500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-119000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-701200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>522300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-133200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>37800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>65100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>95700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-22800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>25900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-65100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>67700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-16500</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10623,8 +10872,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10704,123 +10953,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>599100</v>
+      </c>
+      <c r="E102" s="3">
         <v>81600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-76700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>77400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-74900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>85400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-67700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-152800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>158900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-65300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-125200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>47100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-68700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>318800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-621300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>589100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>42700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-21000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-95300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>105800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-33400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-26100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>59500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>19300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>7800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-12100</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>14500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
   <si>
     <t>DY</t>
   </si>
@@ -656,545 +656,558 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46144</v>
+      </c>
+      <c r="E7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45955</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45864</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45773</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45682</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45591</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45500</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45409</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45318</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45227</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45136</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45045</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44954</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44863</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44772</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44590</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44499</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44317</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44226</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44128</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44037</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43946</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43855</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43764</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43673</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43582</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43491</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43400</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43309</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43218</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43127</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43036</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42945</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42854</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42763</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42672</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1964800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1457600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1451800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1377900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1258600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1084500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1272000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1203100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1142400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>952500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1136100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1041500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1045500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>917500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1042400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>972300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>876300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>761500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>854000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>787600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>727500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>750700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>810300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>823900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>814300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>737600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>884100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>884200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>833700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>748600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>848200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>799500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>731400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>655100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>756200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>780200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>786300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>701100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>799200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>789200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1578100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1192600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1131600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1070500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1011100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>887900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1007400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>952900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>921600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>791400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>886700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>830400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>853400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>765700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>850900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>798000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>745700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>656600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>705900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>651400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>620000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>645500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>658400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>658000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>680200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>633200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>724400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>720400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>701800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>633300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>687200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>642400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>599600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>540600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>600800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>606900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>621500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>561400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>615000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>605900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>386700</v>
+      </c>
+      <c r="E10" s="3">
         <v>264900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>320200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>307500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>247500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>196600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>264600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>250200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>220800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>161100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>249400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>211100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>192100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>151800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>191500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>174300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>130600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>104900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>148100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>136200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>107500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>105200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>151900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>165900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>134100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>104400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>159700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>163800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>131900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>115300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>161000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>157100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>131800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>114500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>155400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>173300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>164800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>139700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>184200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>183300</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1237,8 +1250,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1359,8 +1373,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1481,55 +1498,58 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E14" s="3">
         <v>24000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-10100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-9800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-4000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-7200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-12400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-4600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-8400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-7600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-7800</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1537,33 +1557,33 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>40800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>100</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1576,8 +1596,8 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1591,142 +1611,148 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
-      <c r="AM14" s="3" t="s">
-        <v>8</v>
+      <c r="AM14" s="3">
+        <v>0</v>
       </c>
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>111600</v>
+      </c>
+      <c r="E15" s="3">
         <v>88200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>62200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>60900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>58400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>54800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>52000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>46600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>45200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>45300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>42500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>38000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>37300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>36700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>35500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>35300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>36600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>37300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>37800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>38500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>39100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>43600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>42300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>44100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>45900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>46600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>47400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>47200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>46300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>45900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>45500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>44800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>43400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>42400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>42700</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>40200</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>37400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>35700</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>34500</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1766,252 +1792,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1821000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1389700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1301100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1238100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1173200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1019500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1166000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1099000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1061400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>909700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1016700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>953200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>973000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>874400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>965100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>906700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>851700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>757800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>810500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>754600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>726200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>753000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>763300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>769900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>832700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>740900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>841600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>832700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>806700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>752700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>801500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>751700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>705200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>643400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>708100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>706700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>720200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>655300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>709700</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>704100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>143800</v>
+      </c>
+      <c r="E18" s="3">
         <v>67900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>150700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>139800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>85400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>65100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>106000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>104000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>81000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>42800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>119400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>88300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>72500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>43100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>77300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>65600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>24600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>43500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>33000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>47000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>54000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-18400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>42500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>51500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>27000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>46700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>47800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>26200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>11700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>48100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>73500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>66100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>45800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>89500</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2054,618 +2087,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E20" s="3">
         <v>2900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>4000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>4100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>7700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>5900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>6000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>4800</v>
-      </c>
-      <c r="AN20" s="3">
-        <v>1000</v>
       </c>
       <c r="AO20" s="3">
         <v>1000</v>
       </c>
       <c r="AP20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AQ20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>251900</v>
+      </c>
+      <c r="E21" s="3">
         <v>153200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>211400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>197400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>141300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>118800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>156700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>148900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>123100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>87500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>160500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>124500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>106900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>80200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>115200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>103500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>66000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>41200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>81800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>72500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>43100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>42000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>93000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>101300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>28600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>43900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>91300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>102700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>79100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>43000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>95100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>96700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>77200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>54400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>96700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>119800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>108300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>82600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>125000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>124700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E22" s="3">
         <v>23100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>9100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>9100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>9300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>5900</v>
-      </c>
-      <c r="X22" s="3">
-        <v>4700</v>
       </c>
       <c r="Y22" s="3">
         <v>4700</v>
       </c>
       <c r="Z22" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AA22" s="3">
         <v>7900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>12500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>12600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>13100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>12900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>12200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>12400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>11300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>10400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>9900</v>
-      </c>
-      <c r="AK22" s="3">
-        <v>9700</v>
       </c>
       <c r="AL22" s="3">
         <v>9700</v>
       </c>
       <c r="AM22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AN22" s="3">
         <v>9400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>9200</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>9100</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>106700</v>
+      </c>
+      <c r="E23" s="3">
         <v>17900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>140300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>131100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>78600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>44200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>91300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>94800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>77400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>31800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>112400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>81800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>66100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>31900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>69200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>58900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-4900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>34900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>46000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>49300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-29700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-15300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>30800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>42600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>20500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>38300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>41400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>23700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>44400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>69800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>61500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>37700</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>81400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>33900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>33600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>17600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>21500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>26400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>28600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>21500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>15000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-5700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>12000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>12200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>12700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>10500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>11500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>15600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>26100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>22800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>14000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>30300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>29600</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2786,252 +2835,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E26" s="3">
         <v>16300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>106400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>97500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>61000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>32700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>69800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>68400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>62600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>23400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>83700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>60200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>51500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>54000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>43900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>19500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>28700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>18200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>33900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>37000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-32400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>24200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>29900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>14300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-12100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>27800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>29900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>7900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>28800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>43700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>38800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>23700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>51100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E27" s="3">
         <v>16300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>106400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>97500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>61000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>32700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>69800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>68400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>62600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>23400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>83700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>60200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>51500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>24800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>54000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>43900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>19500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>28700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>18200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>33900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>37000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-32400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-10100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>24200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>29900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>14300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-12100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>27800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>29900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>7900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>28800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>43700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>38800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>23700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>51100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3152,8 +3210,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3199,8 +3260,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -3217,35 +3278,35 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>2600</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3253,12 +3314,12 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>32200</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3274,8 +3335,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3396,8 +3460,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3518,252 +3585,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="AN32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AO32" s="3">
         <v>-1000</v>
       </c>
       <c r="AP32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AQ32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E33" s="3">
         <v>16300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>106400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>97500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>61000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>32700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>69800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>68400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>62600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>23400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>83700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>60200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>51500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>24800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>54000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>43900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>19500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>28700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>18200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>33900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>37000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-32400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>24200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>29900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>14300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-12100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>27800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>29900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>40100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>28800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>43700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>38800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>23700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>51100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3884,257 +3960,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E35" s="3">
         <v>16300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>106400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>97500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>61000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>32700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>69800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>68400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>62600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>23400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>83700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>60200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>51500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>24800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>54000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>43900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>19500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>28700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>18200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>33900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>37000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-32400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>24200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>29900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>14300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-12100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>27800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>29900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>40100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>28800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>43700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>38800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>23700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>51100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46144</v>
+      </c>
+      <c r="E38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45955</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45864</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45773</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45682</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45591</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45500</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45409</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45318</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45227</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45136</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45045</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44954</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44863</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44772</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44590</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44499</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44317</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44226</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44128</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44037</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43946</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43855</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43764</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43673</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43582</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43491</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43400</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43309</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43218</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43127</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43036</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42945</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42854</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42763</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42672</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4177,8 +4262,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4221,172 +4307,176 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>538800</v>
+      </c>
+      <c r="E41" s="3">
         <v>709200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>110100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>28500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>92700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>26100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>101100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>83400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>71400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>224200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>65300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>120300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>185600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>310800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>263700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>261900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>330600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>11800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>22500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>643900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>54600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>33600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>128300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>21500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>23900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>57900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>84000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>24500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>38600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>19400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>29500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>21700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E42" s="3">
         <v>11000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>10400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>11300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>15200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>22300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>21000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>20200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>20000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>22300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>20400</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4465,252 +4555,261 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2239200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1879200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1755800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1744900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1631500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1441300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1723700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1588000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1442300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1298700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1535000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1303400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1243600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1114900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1297800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1170700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1043300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>933200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1077900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1102800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1048500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1057000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1144300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1156600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1145800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1073600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1262900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1156800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1001900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>844600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1003300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>863500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>763100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>332600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>349600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>377300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>355100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>335500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>329800</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>143300</v>
+      </c>
+      <c r="E44" s="3">
         <v>128300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>120100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>122600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>133000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>127300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>116000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>101200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>104000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>108600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>114000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>117200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>115700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>115000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>107100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>98900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>94100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>81300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>69900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>69700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>71100</v>
-      </c>
-      <c r="X44" s="3">
-        <v>70800</v>
       </c>
       <c r="Y44" s="3">
         <v>70800</v>
       </c>
       <c r="Z44" s="3">
+        <v>70800</v>
+      </c>
+      <c r="AA44" s="3">
         <v>77800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>92600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>98300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>104900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>107400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>105200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>94400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>90800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>87800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>84300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>448500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>490400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>472500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>529100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>481600</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>570000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>450600</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4750,211 +4849,217 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>38600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>42800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>43900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>47000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>30900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>37500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>43300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>47900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>29000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>38400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>49700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>48600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>31800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>32300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>31100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>37800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>29100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>33300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>30100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>30800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>39700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>28800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>50100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>46700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>41700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>45400</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2970400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2756900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2026000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1938900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1824700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1694600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1896800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1760700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1626800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1550000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1708700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1555200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1483800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1492700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1513000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1433800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1370000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1356100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1449000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1477700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1498100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1168600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1265500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1306600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1930900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1258300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1411900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1307800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1178500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1096400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1148900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1005300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>936100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>904800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>893400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>938500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>950200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>888300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>966900</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>851200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4994,63 +5099,63 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
         <v>8300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>12500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>14100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>15300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>16700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>16200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>17600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>18600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>19900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>21300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>22700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>24200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>26200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>28400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>55200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>32000</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
@@ -5075,252 +5180,261 @@
       <c r="AP47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>767800</v>
+      </c>
+      <c r="E48" s="3">
         <v>745000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>686700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>676800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>679400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>654100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>622800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>563000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>538700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>521300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>505100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>466000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>447100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>435100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>403300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>377600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>361100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>355900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>346200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>343600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>340500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>337100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>354200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>385500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>422100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>446200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>463000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>491700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>498400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>424800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>428300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>423700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>416300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>414800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>423300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>422100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>378400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>344100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>337700</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2324700</v>
+      </c>
+      <c r="E49" s="3">
         <v>2369400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>572200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>582000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>538300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>550100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>560000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>429500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>423800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>420900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>425700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>352100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>355600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>359100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>362600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>366500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>370400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>374300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>378300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>382500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>387100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>391800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>397000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>402000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>407200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>465700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>470900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>476200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>481500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>486900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>492300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>498100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>503900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>493200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>499100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>505300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>513100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>498200</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>500300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>508000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5441,8 +5555,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5563,130 +5680,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>97300</v>
+        <v>41700</v>
       </c>
       <c r="E52" s="3">
+        <v>35600</v>
+      </c>
+      <c r="F52" s="3">
         <v>35900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>58000</v>
       </c>
-      <c r="H52" s="3">
-        <v>41600</v>
-      </c>
       <c r="I52" s="3">
+        <v>11800</v>
+      </c>
+      <c r="J52" s="3">
         <v>29800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>20700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>19000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>16800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>17500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>18100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>17900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>15800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>21400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>21100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>29000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>29700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>30600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>31400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>24800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>25500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>26400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>24400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>34200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>31700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>25400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>26800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>28200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>36800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>33400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>34300</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>35800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>33500</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5807,130 +5930,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6180400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5979200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3324800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3219900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3105000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2945400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3114700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2779400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2611600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2516900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2664200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2395600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2311700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2313300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2305300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2206400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2132100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2118200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2204700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2241900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2263000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1944200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2065100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2144700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2812900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2217600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2395600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2328400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2211200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2097500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2133200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1952400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1883000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1841000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1852500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1899300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1876000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1766400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1838400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>1719700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5973,8 +6102,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6017,171 +6147,175 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>666600</v>
+      </c>
+      <c r="E57" s="3">
         <v>497300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>297100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>264900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>259200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>223500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>241000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>233500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>212900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>222100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>215300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>204800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>196200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>207700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>201000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>187600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>176400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>155900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>173600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>173200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>171000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>159000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>183700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>177300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>194400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>119600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>129500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>140300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>138700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>119500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>134700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>125700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>112200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>92400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>109900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>133000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>119300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>99300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>114700</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>115500</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E58" s="3">
         <v>46300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>58100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>59200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>53200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>45800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>39800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>33300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>50400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>49500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>47600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>46800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>46100</v>
-      </c>
-      <c r="P58" s="3">
-        <v>17500</v>
       </c>
       <c r="Q58" s="3">
         <v>17500</v>
@@ -6196,22 +6330,22 @@
         <v>17500</v>
       </c>
       <c r="U58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="V58" s="3">
         <v>13100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>66600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>61500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>81700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>78100</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>22500</v>
       </c>
       <c r="AA58" s="3">
         <v>22500</v>
@@ -6223,534 +6357,549 @@
         <v>22500</v>
       </c>
       <c r="AD58" s="3">
+        <v>22500</v>
+      </c>
+      <c r="AE58" s="3">
         <v>16900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>11300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>5600</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
-      </c>
       <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
         <v>31300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>28900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>26500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>24100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>21700</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>14400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>18800</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>17500</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>227500</v>
+      </c>
+      <c r="E59" s="3">
         <v>207200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>103500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>110800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>173600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>141700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>136900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>67600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>103600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>73700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>61700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>57400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>68100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>244300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>252600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>227100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>201700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>208400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>206400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>207600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>203500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>207800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>201900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>211500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>211400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>180900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>212800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>199800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>191700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>159900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>169300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>153300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>134800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>140800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>149200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>163900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>155100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>145000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>179700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1149400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1006900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>656500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>612700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>631800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>587200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>608500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>511100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>513600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>506300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>488800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>459400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>433100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>469600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>471100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>432100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>395700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>381800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>393200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>447500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>436100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>448500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>463700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>411300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>428300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>323000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>364800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>357000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>341700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>285000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>304000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>310300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>275900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>259600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>283100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>318500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>288900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>263200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>312000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>322600</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2948200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2945700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1006500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1087600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1092500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1010100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1165700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>988600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>889500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>835500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>993300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>842600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>846900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>807400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>811400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>815300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>819300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>823300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>827200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>831200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>835200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>501600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>490000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>665500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1363900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>844400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>970200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>932300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>867400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>867600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>867800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>727300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>731700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>733800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>736000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>738300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>811600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>740600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>774500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>706200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>90700</v>
+      </c>
+      <c r="E62" s="3">
         <v>82300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>93500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>82200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>82400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>76800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>75100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>77300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>76200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>70800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>70200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>68300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>72100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>167600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>164200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>161900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>158800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>154600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>173500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>182700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>181800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>182800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>198200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>194100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>186800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>181600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>180400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>185700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>181000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>140800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>144500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>131500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>128400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>122500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>143800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>170900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>152800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>147600</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>138200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6871,8 +7020,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6993,8 +7145,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7115,130 +7270,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4284700</v>
+      </c>
+      <c r="E66" s="3">
         <v>4120000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1841500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1850200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1838800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1706300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1881000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1620900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1531000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1462200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1610200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1431600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1414300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1444500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1446700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1409400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1373800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1359700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1393900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1461400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1453100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1132900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1151900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1270900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1979000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1349000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1515400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1474900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1390000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1293300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1316400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1169200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1136000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1116000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1162900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1227700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1253300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1151400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1224700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1162400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7281,8 +7442,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7403,8 +7565,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7525,8 +7690,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7647,8 +7815,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7769,130 +7940,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1558800</v>
+      </c>
+      <c r="E72" s="3">
         <v>1467500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1451300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1344900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1247400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1220400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1201300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1131500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1063100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1040300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1026600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>942800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>882600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>855100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>838300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>784300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>747100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>748400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>798500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>769800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>797700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>800600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>867800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>833800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>796800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>829700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>840900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>816700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>786800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>772500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>784500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>756700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>726800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>709600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>674200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>652300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>608600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>600500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>588900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>537900</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8013,8 +8190,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8135,8 +8315,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8257,130 +8440,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1895700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1859100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1483300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1369700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1266200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1239100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1233700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1158400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1080600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1054700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1053900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>964000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>897400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>868800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>858600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>797000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>758300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>758500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>810800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>780400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>810000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>811300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>913100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>873700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>833900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>868600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>880200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>853400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>821200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>804200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>816900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>783200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>747000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>725000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>689600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>671600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>622700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>615100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>613700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>557300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8501,257 +8690,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46144</v>
+      </c>
+      <c r="E80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45955</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45864</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45773</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45682</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45591</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45500</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45409</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45318</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45227</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45136</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45045</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44954</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44863</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44772</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44590</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44499</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44317</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44226</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44128</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44037</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43946</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43855</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43764</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43673</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43582</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43491</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43400</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43309</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43218</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43127</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43036</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42945</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42854</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42763</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42672</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E81" s="3">
         <v>16300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>106400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>97500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>61000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>32700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>69800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>68400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>62600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>23400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>83700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>60200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>51500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>24800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>54000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>43900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>19500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>28700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>18200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>33900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>37000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-32400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>24200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>29900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>14300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-12100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>27800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>29900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>40100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>28800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>43700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>38800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>23700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>51100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8794,130 +8992,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E83" s="3">
         <v>44700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>42500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>40600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>39400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>38500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>36500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>33800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>33100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>31600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>31400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>32700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>36700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>35500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>35300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>36600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>37300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>37800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>38500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>39100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>43600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>42300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>44100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>45900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>46600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>47400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>47200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>46300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>45900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>45500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>44800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>43400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>42400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>42700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>40200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>37400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>35700</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>34500</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9038,8 +9240,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9160,8 +9365,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9282,8 +9490,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9404,8 +9615,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9526,130 +9740,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E89" s="3">
         <v>419000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>220000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>57400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-54000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>328200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>65800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-37400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>325100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-37300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>56300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-85100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>246200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-12000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-64900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>145500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>104300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>17300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>41500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>102400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>111900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>82300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>85200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>191800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-24000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-53600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-56100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>142800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-55500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>12600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>24600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>103700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>56800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>149900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>42300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>105800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-41600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>182500</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9692,130 +9912,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-70300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-54400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-55200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-51700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-79500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-68500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-74600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-65400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-42000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-57400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-67200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-51000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-42900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-65200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-54800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-42500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-38400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-43600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-45100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-36700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-31600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-21900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-9400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-18700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-17900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-45800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-47300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-31800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-58300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-40100</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-47300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9936,8 +10160,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10058,130 +10285,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1680500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-47600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-39100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-68600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-59800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-216500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-76700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-42200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-52700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-179900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-40000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-33600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-62600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-49200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-39100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-33000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-43400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-44100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-35500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-28600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-20400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-18300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-15800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-14500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-32500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-42600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-39100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-45800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-78400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-32900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-38200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-151600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10224,8 +10457,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10265,8 +10499,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10346,8 +10580,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10468,8 +10705,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10590,8 +10830,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10712,130 +10955,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-65400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1860500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-90800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>45900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-191000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>146400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>77700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-187000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>149500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-34100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-14200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-27200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-55100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-58400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-50400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>305900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-85500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-119000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-701200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>522300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-133200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>37800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>65100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>95700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-22800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>25900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-65100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>67700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-16500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10875,8 +11124,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10956,126 +11205,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-170300</v>
+      </c>
+      <c r="E102" s="3">
         <v>599100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>81600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-76700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>77400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-74900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>85400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-67700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>12000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-152800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>158900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-55000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-65300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-125200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>47100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-68700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>318800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-10500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-621300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>589100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>42700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-21000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-95300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>105800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-33400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-26100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>59500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>19300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>7800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-12100</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>14500</v>
       </c>
     </row>
